--- a/機種名変換.xlsx
+++ b/機種名変換.xlsx
@@ -554,7 +554,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1094"/>
+  <dimension ref="B1:C1095"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
     <col width="8.796875" customWidth="1" style="1" min="1" max="1"/>
@@ -13648,42 +13648,53 @@
       </c>
     </row>
     <row r="1092" customFormat="1" s="1">
-      <c r="B1092" t="inlineStr">
+      <c r="B1092" s="0" t="inlineStr">
         <is>
           <t>Lタコスロ</t>
         </is>
       </c>
-      <c r="C1092" t="inlineStr">
+      <c r="C1092" s="0" t="inlineStr">
         <is>
           <t>タコスロ</t>
         </is>
       </c>
     </row>
     <row r="1093" customFormat="1" s="1">
-      <c r="B1093" t="inlineStr">
+      <c r="B1093" s="0" t="inlineStr">
         <is>
           <t>Lモグモグ風林火山 大海戦の巻</t>
         </is>
       </c>
-      <c r="C1093" t="inlineStr">
+      <c r="C1093" s="0" t="inlineStr">
         <is>
           <t>モグモグ大海戦</t>
         </is>
       </c>
     </row>
     <row r="1094" customFormat="1" s="1">
-      <c r="B1094" t="inlineStr">
+      <c r="B1094" s="0" t="inlineStr">
         <is>
           <t>L青ブタ</t>
         </is>
       </c>
-      <c r="C1094" t="inlineStr">
+      <c r="C1094" s="0" t="inlineStr">
         <is>
           <t>青ブタ</t>
         </is>
       </c>
     </row>
-    <row r="1095" customFormat="1" s="1"/>
+    <row r="1095" customFormat="1" s="1">
+      <c r="B1095" s="0" t="inlineStr">
+        <is>
+          <t>L少女歌劇レヴュースタァライト</t>
+        </is>
+      </c>
+      <c r="C1095" s="0" t="inlineStr">
+        <is>
+          <t>レヴュースタァライト</t>
+        </is>
+      </c>
+    </row>
     <row r="1096" customFormat="1" s="1"/>
     <row r="1097" customFormat="1" s="1"/>
     <row r="1098" customFormat="1" s="1"/>

--- a/機種名変換.xlsx
+++ b/機種名変換.xlsx
@@ -554,7 +554,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:C1183"/>
+  <dimension ref="A1:C1184"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
     <col width="8.796875" customWidth="1" style="1" min="1" max="1"/>
@@ -13696,1058 +13696,1070 @@
       </c>
     </row>
     <row r="1096" customFormat="1" s="1">
-      <c r="B1096" t="inlineStr">
+      <c r="B1096" s="0" t="inlineStr">
         <is>
           <t>L 無職転生 ~異世界行ったら本気だす~</t>
         </is>
       </c>
-      <c r="C1096" t="inlineStr">
+      <c r="C1096" s="0" t="inlineStr">
         <is>
           <t>無職転生</t>
         </is>
       </c>
     </row>
     <row r="1097" customFormat="1" s="1">
-      <c r="B1097" t="inlineStr">
+      <c r="B1097" s="0" t="inlineStr">
         <is>
           <t>LBパチスロ ヱヴァンゲリヲン ~約束の扉~</t>
         </is>
       </c>
-      <c r="C1097" t="inlineStr">
+      <c r="C1097" s="0" t="inlineStr">
         <is>
           <t>ヱヴァ約束</t>
         </is>
       </c>
     </row>
     <row r="1098" customFormat="1" s="1">
-      <c r="B1098" t="inlineStr">
+      <c r="B1098" s="0" t="inlineStr">
         <is>
           <t>Lパチスロ かぐや様は告らせたい</t>
         </is>
       </c>
-      <c r="C1098" t="inlineStr">
+      <c r="C1098" s="0" t="inlineStr">
         <is>
           <t>かぐや様</t>
         </is>
       </c>
     </row>
     <row r="1099" customFormat="1" s="1">
-      <c r="B1099" t="inlineStr">
+      <c r="B1099" s="0" t="inlineStr">
         <is>
           <t>Lラブ嬢3~Wご指名はいかがですか?~</t>
         </is>
       </c>
-      <c r="C1099" t="inlineStr">
+      <c r="C1099" s="0" t="inlineStr">
         <is>
           <t>ラブ嬢3</t>
         </is>
       </c>
     </row>
     <row r="1100" customFormat="1" s="1">
-      <c r="B1100" t="inlineStr">
+      <c r="B1100" s="0" t="inlineStr">
         <is>
           <t>クレアの秘宝伝 ~はじまりの扉と太陽の石~ ボーナストリガーver.</t>
         </is>
       </c>
-      <c r="C1100" t="inlineStr">
+      <c r="C1100" s="0" t="inlineStr">
         <is>
           <t>クレアの秘宝伝</t>
         </is>
       </c>
     </row>
     <row r="1101" customFormat="1" s="1">
-      <c r="B1101" t="inlineStr">
+      <c r="B1101" s="0" t="inlineStr">
         <is>
           <t>スマスロ 吉宗</t>
         </is>
       </c>
-      <c r="C1101" t="inlineStr">
+      <c r="C1101" s="0" t="inlineStr">
         <is>
           <t>吉宗</t>
         </is>
       </c>
     </row>
     <row r="1102" customFormat="1" s="1">
-      <c r="B1102" t="inlineStr">
+      <c r="B1102" s="0" t="inlineStr">
         <is>
           <t>L BIRDIE WING -Golf Girls Story-</t>
         </is>
       </c>
-      <c r="C1102" t="inlineStr">
+      <c r="C1102" s="0" t="inlineStr">
         <is>
           <t>BIRDIE WING</t>
         </is>
       </c>
     </row>
     <row r="1103" customFormat="1" s="1">
-      <c r="B1103" t="inlineStr">
+      <c r="B1103" s="0" t="inlineStr">
         <is>
           <t>Lスマスロ ゴッドイーター リザレクション</t>
         </is>
       </c>
-      <c r="C1103" t="inlineStr">
+      <c r="C1103" s="0" t="inlineStr">
         <is>
           <t>ゴッドイーター</t>
         </is>
       </c>
     </row>
     <row r="1104" customFormat="1" s="1">
-      <c r="B1104" t="inlineStr">
+      <c r="B1104" s="0" t="inlineStr">
         <is>
           <t>Lスマスロ モンキーターンV</t>
         </is>
       </c>
-      <c r="C1104" t="inlineStr">
+      <c r="C1104" s="0" t="inlineStr">
         <is>
           <t>モンキーターンV</t>
         </is>
       </c>
     </row>
     <row r="1105" customFormat="1" s="1">
-      <c r="B1105" t="inlineStr">
+      <c r="B1105" s="0" t="inlineStr">
         <is>
           <t>Lスマスロかぐや様は告らせたい</t>
         </is>
       </c>
-      <c r="C1105" t="inlineStr">
+      <c r="C1105" s="0" t="inlineStr">
         <is>
           <t>かぐや様</t>
         </is>
       </c>
     </row>
     <row r="1106" customFormat="1" s="1">
-      <c r="B1106" t="inlineStr">
+      <c r="B1106" s="0" t="inlineStr">
         <is>
           <t>Lスマスロ北斗の拳</t>
         </is>
       </c>
-      <c r="C1106" t="inlineStr">
+      <c r="C1106" s="0" t="inlineStr">
         <is>
           <t>スマスロ北斗の拳</t>
         </is>
       </c>
     </row>
     <row r="1107" customFormat="1" s="1">
-      <c r="B1107" t="inlineStr">
+      <c r="B1107" s="0" t="inlineStr">
         <is>
           <t>Lスロット ゾンビランドサガ</t>
         </is>
       </c>
-      <c r="C1107" t="inlineStr">
+      <c r="C1107" s="0" t="inlineStr">
         <is>
           <t>ゾンビランドサガ</t>
         </is>
       </c>
     </row>
     <row r="1108" customFormat="1" s="1">
-      <c r="B1108" t="inlineStr">
+      <c r="B1108" s="0" t="inlineStr">
         <is>
           <t>Lビッグドリーム THE GOLDEN PUSHER</t>
         </is>
       </c>
-      <c r="C1108" t="inlineStr">
+      <c r="C1108" s="0" t="inlineStr">
         <is>
           <t>ビッグドリーム</t>
         </is>
       </c>
     </row>
     <row r="1109" customFormat="1" s="1">
-      <c r="B1109" t="inlineStr">
+      <c r="B1109" s="0" t="inlineStr">
         <is>
           <t>Lミリオンゴッド-神々の軌跡-</t>
         </is>
       </c>
-      <c r="C1109" t="inlineStr">
+      <c r="C1109" s="0" t="inlineStr">
         <is>
           <t>ゴッド神々の軌跡</t>
         </is>
       </c>
     </row>
     <row r="1110" customFormat="1" s="1">
-      <c r="B1110" t="inlineStr">
+      <c r="B1110" s="0" t="inlineStr">
         <is>
           <t>ストリートファイター6</t>
         </is>
       </c>
-      <c r="C1110" t="inlineStr">
+      <c r="C1110" s="0" t="inlineStr">
         <is>
           <t>スト6</t>
         </is>
       </c>
     </row>
     <row r="1111" customFormat="1" s="1">
-      <c r="B1111" t="inlineStr">
+      <c r="B1111" s="0" t="inlineStr">
         <is>
           <t>ソードアート・オンラインII</t>
         </is>
       </c>
-      <c r="C1111" t="inlineStr">
+      <c r="C1111" s="0" t="inlineStr">
         <is>
           <t>SAOII</t>
         </is>
       </c>
     </row>
     <row r="1112" customFormat="1" s="1">
-      <c r="B1112" t="inlineStr">
+      <c r="B1112" s="0" t="inlineStr">
         <is>
           <t>ワールドダイスター</t>
         </is>
       </c>
-      <c r="C1112" t="inlineStr">
+      <c r="C1112" s="0" t="inlineStr">
         <is>
           <t>ワールドダイスター</t>
         </is>
       </c>
     </row>
     <row r="1113" customFormat="1" s="1">
-      <c r="B1113" t="inlineStr">
+      <c r="B1113" s="0" t="inlineStr">
         <is>
           <t>異世界かるてっと</t>
         </is>
       </c>
-      <c r="C1113" t="inlineStr">
+      <c r="C1113" s="0" t="inlineStr">
         <is>
           <t>異世界かるてっと</t>
         </is>
       </c>
     </row>
     <row r="1114" customFormat="1" s="1">
-      <c r="B1114" t="inlineStr">
+      <c r="B1114" s="0" t="inlineStr">
         <is>
           <t>邪神ちゃんドロップキック</t>
         </is>
       </c>
-      <c r="C1114" t="inlineStr">
+      <c r="C1114" s="0" t="inlineStr">
         <is>
           <t>邪神ちゃん</t>
         </is>
       </c>
     </row>
     <row r="1115" customFormat="1" s="1">
-      <c r="B1115" t="inlineStr">
+      <c r="B1115" s="0" t="inlineStr">
         <is>
           <t>L A-SLOT+このすば FX</t>
         </is>
       </c>
-      <c r="C1115" t="inlineStr">
+      <c r="C1115" s="0" t="inlineStr">
         <is>
           <t>Aこのすば</t>
         </is>
       </c>
     </row>
     <row r="1116" customFormat="1" s="1">
-      <c r="B1116" t="inlineStr">
+      <c r="B1116" s="0" t="inlineStr">
         <is>
           <t>L スマスロ リコリス・リコイル KX</t>
         </is>
       </c>
-      <c r="C1116" t="inlineStr">
+      <c r="C1116" s="0" t="inlineStr">
         <is>
           <t>リコリス</t>
         </is>
       </c>
     </row>
     <row r="1117" customFormat="1" s="1">
-      <c r="B1117" t="inlineStr">
+      <c r="B1117" s="0" t="inlineStr">
         <is>
           <t>L スマスロ化物語 KH</t>
         </is>
       </c>
-      <c r="C1117" t="inlineStr">
+      <c r="C1117" s="0" t="inlineStr">
         <is>
           <t>スマスロ化物語</t>
         </is>
       </c>
     </row>
     <row r="1118" customFormat="1" s="1">
-      <c r="B1118" t="inlineStr">
+      <c r="B1118" s="0" t="inlineStr">
         <is>
           <t>L スマスロ北斗の拳 転生の章2 MW</t>
         </is>
       </c>
-      <c r="C1118" t="inlineStr">
+      <c r="C1118" s="0" t="inlineStr">
         <is>
           <t>北斗転生2</t>
         </is>
       </c>
     </row>
     <row r="1119" customFormat="1" s="1">
-      <c r="B1119" t="inlineStr">
+      <c r="B1119" s="0" t="inlineStr">
         <is>
           <t>L スマスロ攻殻機動隊 ZS</t>
         </is>
       </c>
-      <c r="C1119" t="inlineStr">
+      <c r="C1119" s="0" t="inlineStr">
         <is>
           <t>L攻殻機動隊</t>
         </is>
       </c>
     </row>
     <row r="1120" customFormat="1" s="1">
-      <c r="B1120" t="inlineStr">
+      <c r="B1120" s="0" t="inlineStr">
         <is>
           <t>L スマスロ東京リベンジャーズ ZF</t>
         </is>
       </c>
-      <c r="C1120" t="inlineStr">
+      <c r="C1120" s="0" t="inlineStr">
         <is>
           <t>東京リベンジャーズ</t>
         </is>
       </c>
     </row>
     <row r="1121" customFormat="1" s="1">
-      <c r="B1121" t="inlineStr">
+      <c r="B1121" s="0" t="inlineStr">
         <is>
           <t>L スマスロ頭文字D2nd YR</t>
         </is>
       </c>
-      <c r="C1121" t="inlineStr">
+      <c r="C1121" s="0" t="inlineStr">
         <is>
           <t>頭文字D2</t>
         </is>
       </c>
     </row>
     <row r="1122" customFormat="1" s="1">
-      <c r="B1122" t="inlineStr">
+      <c r="B1122" s="0" t="inlineStr">
         <is>
           <t>L ビッグドリーム KR</t>
         </is>
       </c>
-      <c r="C1122" t="inlineStr">
+      <c r="C1122" s="0" t="inlineStr">
         <is>
           <t>ビッグドリーム</t>
         </is>
       </c>
     </row>
     <row r="1123" customFormat="1" s="1">
-      <c r="B1123" t="inlineStr">
+      <c r="B1123" s="0" t="inlineStr">
         <is>
           <t>L 甲鉄城のカバネリ 海門決戦 XX</t>
         </is>
       </c>
-      <c r="C1123" t="inlineStr">
+      <c r="C1123" s="0" t="inlineStr">
         <is>
           <t>カバネリ海門決戦</t>
         </is>
       </c>
     </row>
     <row r="1124" customFormat="1" s="1">
-      <c r="B1124" t="inlineStr">
+      <c r="B1124" s="0" t="inlineStr">
         <is>
           <t>L 防振り FN</t>
         </is>
       </c>
-      <c r="C1124" t="inlineStr">
+      <c r="C1124" s="0" t="inlineStr">
         <is>
           <t>防振り</t>
         </is>
       </c>
     </row>
     <row r="1125" customFormat="1" s="1">
-      <c r="B1125" t="inlineStr">
+      <c r="B1125" s="0" t="inlineStr">
         <is>
           <t>L/いざ番長/SB8</t>
         </is>
       </c>
-      <c r="C1125" t="inlineStr">
+      <c r="C1125" s="0" t="inlineStr">
         <is>
           <t>いざ!番長</t>
         </is>
       </c>
     </row>
     <row r="1126" customFormat="1" s="1">
-      <c r="B1126" t="inlineStr">
+      <c r="B1126" s="0" t="inlineStr">
         <is>
           <t>L/スマスロマギアレコード/RN</t>
         </is>
       </c>
-      <c r="C1126" t="inlineStr">
+      <c r="C1126" s="0" t="inlineStr">
         <is>
           <t>マギレコ</t>
         </is>
       </c>
     </row>
     <row r="1127" customFormat="1" s="1">
-      <c r="B1127" t="inlineStr">
+      <c r="B1127" s="0" t="inlineStr">
         <is>
           <t>L/ハナビ/KM</t>
         </is>
       </c>
-      <c r="C1127" t="inlineStr">
+      <c r="C1127" s="0" t="inlineStr">
         <is>
           <t>Lハナビ</t>
         </is>
       </c>
     </row>
     <row r="1128">
-      <c r="B1128" t="inlineStr">
+      <c r="B1128" s="0" t="inlineStr">
         <is>
           <t>L/バジリスク絆2~天膳~/ZN</t>
         </is>
       </c>
-      <c r="C1128" t="inlineStr">
+      <c r="C1128" s="0" t="inlineStr">
         <is>
           <t>バジ絆2天膳</t>
         </is>
       </c>
     </row>
     <row r="1129">
-      <c r="B1129" t="inlineStr">
+      <c r="B1129" s="0" t="inlineStr">
         <is>
           <t>L/ミリオンゴッド/CX</t>
         </is>
       </c>
-      <c r="C1129" t="inlineStr">
+      <c r="C1129" s="0" t="inlineStr">
         <is>
           <t>ゴッド神々の軌跡</t>
         </is>
       </c>
     </row>
     <row r="1130">
-      <c r="B1130" t="inlineStr">
+      <c r="B1130" s="0" t="inlineStr">
         <is>
           <t>L/ヨシムネS/SC2</t>
         </is>
       </c>
-      <c r="C1130" t="inlineStr">
+      <c r="C1130" s="0" t="inlineStr">
         <is>
           <t>吉宗</t>
         </is>
       </c>
     </row>
     <row r="1131">
-      <c r="B1131" t="inlineStr">
+      <c r="B1131" s="0" t="inlineStr">
         <is>
           <t>L/ワールドダイスター/PA3</t>
         </is>
       </c>
-      <c r="C1131" t="inlineStr">
+      <c r="C1131" s="0" t="inlineStr">
         <is>
           <t>ワールドダイスター</t>
         </is>
       </c>
     </row>
     <row r="1132">
-      <c r="B1132" t="inlineStr">
+      <c r="B1132" s="0" t="inlineStr">
         <is>
           <t>L/真打吉宗/A1</t>
         </is>
       </c>
-      <c r="C1132" t="inlineStr">
+      <c r="C1132" s="0" t="inlineStr">
         <is>
           <t>真打吉宗</t>
         </is>
       </c>
     </row>
     <row r="1133">
-      <c r="B1133" t="inlineStr">
+      <c r="B1133" s="0" t="inlineStr">
         <is>
           <t>L/緑ドン5/FY</t>
         </is>
       </c>
-      <c r="C1133" t="inlineStr">
+      <c r="C1133" s="0" t="inlineStr">
         <is>
           <t>緑ドン</t>
         </is>
       </c>
     </row>
     <row r="1134">
-      <c r="B1134" t="inlineStr">
+      <c r="B1134" s="0" t="inlineStr">
         <is>
           <t>LB 異世界かるてっと KR</t>
         </is>
       </c>
-      <c r="C1134" t="inlineStr">
+      <c r="C1134" s="0" t="inlineStr">
         <is>
           <t>異世界かるてっと</t>
         </is>
       </c>
     </row>
     <row r="1135">
-      <c r="B1135" t="inlineStr">
+      <c r="B1135" s="0" t="inlineStr">
         <is>
           <t>LB/クレアの秘宝伝ボーナストリガーVER./A2</t>
         </is>
       </c>
-      <c r="C1135" t="inlineStr">
+      <c r="C1135" s="0" t="inlineStr">
         <is>
           <t>クレアの秘宝伝</t>
         </is>
       </c>
     </row>
     <row r="1136">
-      <c r="B1136" t="inlineStr">
+      <c r="B1136" s="0" t="inlineStr">
         <is>
           <t>LB/スマスロサンダーVHA</t>
         </is>
       </c>
-      <c r="C1136" t="inlineStr">
+      <c r="C1136" s="0" t="inlineStr">
         <is>
           <t>LBサンダーV</t>
         </is>
       </c>
     </row>
     <row r="1137">
-      <c r="B1137" t="inlineStr">
+      <c r="B1137" s="0" t="inlineStr">
         <is>
           <t>LB/タコスロBD</t>
         </is>
       </c>
-      <c r="C1137" t="inlineStr">
+      <c r="C1137" s="0" t="inlineStr">
         <is>
           <t>タコスロ</t>
         </is>
       </c>
     </row>
     <row r="1138">
-      <c r="B1138" t="inlineStr">
+      <c r="B1138" s="0" t="inlineStr">
         <is>
           <t>LBAREXBRIGHTBA</t>
         </is>
       </c>
-      <c r="C1138" t="inlineStr">
+      <c r="C1138" s="0" t="inlineStr">
         <is>
           <t>アレックスB</t>
         </is>
       </c>
     </row>
     <row r="1139">
-      <c r="B1139" t="inlineStr">
+      <c r="B1139" s="0" t="inlineStr">
         <is>
           <t>LBケロット5ND05H</t>
         </is>
       </c>
-      <c r="C1139" t="inlineStr">
+      <c r="C1139" s="0" t="inlineStr">
         <is>
           <t>ケロット5BT</t>
         </is>
       </c>
     </row>
     <row r="1140">
-      <c r="B1140" t="inlineStr">
+      <c r="B1140" s="0" t="inlineStr">
         <is>
           <t>LBマジカルハロウィンGS</t>
         </is>
       </c>
-      <c r="C1140" t="inlineStr">
+      <c r="C1140" s="0" t="inlineStr">
         <is>
           <t>LBマジハロ</t>
         </is>
       </c>
     </row>
     <row r="1141">
-      <c r="B1141" t="inlineStr">
+      <c r="B1141" s="0" t="inlineStr">
         <is>
           <t>LB翔べ!ハーレムエースCF</t>
         </is>
       </c>
-      <c r="C1141" t="inlineStr">
+      <c r="C1141" s="0" t="inlineStr">
         <is>
           <t>LBハーレムエース</t>
         </is>
       </c>
     </row>
     <row r="1142">
-      <c r="B1142" t="inlineStr">
+      <c r="B1142" s="0" t="inlineStr">
         <is>
           <t>Lかぐや様は告らせたいjA</t>
         </is>
       </c>
-      <c r="C1142" t="inlineStr">
+      <c r="C1142" s="0" t="inlineStr">
         <is>
           <t>かぐや様</t>
         </is>
       </c>
     </row>
     <row r="1143">
-      <c r="B1143" t="inlineStr">
+      <c r="B1143" s="0" t="inlineStr">
         <is>
           <t>Lからくりサーカス2jG</t>
         </is>
       </c>
-      <c r="C1143" t="inlineStr">
+      <c r="C1143" s="0" t="inlineStr">
         <is>
           <t>からくりサーカス2</t>
         </is>
       </c>
     </row>
     <row r="1144">
-      <c r="B1144" t="inlineStr">
+      <c r="B1144" s="0" t="inlineStr">
         <is>
           <t>Lとある科学の超電磁砲2FV</t>
         </is>
       </c>
-      <c r="C1144" t="inlineStr">
+      <c r="C1144" s="0" t="inlineStr">
         <is>
           <t>とある超電磁砲2</t>
         </is>
       </c>
     </row>
     <row r="1145">
-      <c r="B1145" t="inlineStr">
+      <c r="B1145" s="0" t="inlineStr">
         <is>
           <t>Lとある魔術の禁書目録2FA</t>
         </is>
       </c>
-      <c r="C1145" t="inlineStr">
+      <c r="C1145" s="0" t="inlineStr">
         <is>
           <t>とある禁書目録2</t>
         </is>
       </c>
     </row>
     <row r="1146">
-      <c r="B1146" t="inlineStr">
+      <c r="B1146" s="0" t="inlineStr">
         <is>
           <t>Lやじきた道中記参る!BG</t>
         </is>
       </c>
-      <c r="C1146" t="inlineStr">
+      <c r="C1146" s="0" t="inlineStr">
         <is>
           <t>やじきた</t>
         </is>
       </c>
     </row>
     <row r="1147">
-      <c r="B1147" t="inlineStr">
+      <c r="B1147" s="0" t="inlineStr">
         <is>
           <t>Lようこそ実力至上主義の教室へDE</t>
         </is>
       </c>
-      <c r="C1147" t="inlineStr">
+      <c r="C1147" s="0" t="inlineStr">
         <is>
           <t>よう実</t>
         </is>
       </c>
     </row>
     <row r="1148">
-      <c r="B1148" t="inlineStr">
+      <c r="B1148" s="0" t="inlineStr">
         <is>
           <t>LアクダマドライブTP</t>
         </is>
       </c>
-      <c r="C1148" t="inlineStr">
+      <c r="C1148" s="0" t="inlineStr">
         <is>
           <t>アクダマドライブ</t>
         </is>
       </c>
     </row>
     <row r="1149">
-      <c r="B1149" t="inlineStr">
+      <c r="B1149" s="0" t="inlineStr">
         <is>
           <t>LアズールレーンTHE ANIMATION KN</t>
         </is>
       </c>
-      <c r="C1149" t="inlineStr">
+      <c r="C1149" s="0" t="inlineStr">
         <is>
           <t>アズールレーン</t>
         </is>
       </c>
     </row>
     <row r="1150">
-      <c r="B1150" t="inlineStr">
+      <c r="B1150" s="0" t="inlineStr">
         <is>
           <t>LアニマルスロットドッチZT</t>
         </is>
       </c>
-      <c r="C1150" t="inlineStr">
+      <c r="C1150" s="0" t="inlineStr">
         <is>
           <t>アニスロドッチ</t>
         </is>
       </c>
     </row>
     <row r="1151">
-      <c r="B1151" t="inlineStr">
+      <c r="B1151" s="0" t="inlineStr">
         <is>
           <t>Lストリートファイター6SB</t>
         </is>
       </c>
-      <c r="C1151" t="inlineStr">
+      <c r="C1151" s="0" t="inlineStr">
         <is>
           <t>スト6</t>
         </is>
       </c>
     </row>
     <row r="1152">
-      <c r="B1152" t="inlineStr">
+      <c r="B1152" s="0" t="inlineStr">
         <is>
           <t>LスーパーブラックジャックSLDC</t>
         </is>
       </c>
-      <c r="C1152" t="inlineStr">
+      <c r="C1152" s="0" t="inlineStr">
         <is>
           <t>SBJ</t>
         </is>
       </c>
     </row>
     <row r="1153">
-      <c r="B1153" t="inlineStr">
+      <c r="B1153" s="0" t="inlineStr">
         <is>
           <t>LダークハイビSB</t>
         </is>
       </c>
-      <c r="C1153" t="inlineStr">
+      <c r="C1153" s="0" t="inlineStr">
         <is>
           <t>ダークハイビ</t>
         </is>
       </c>
     </row>
     <row r="1154">
-      <c r="B1154" t="inlineStr">
+      <c r="B1154" s="0" t="inlineStr">
         <is>
           <t>LネオプラネットSLED</t>
         </is>
       </c>
-      <c r="C1154" t="inlineStr">
+      <c r="C1154" s="0" t="inlineStr">
         <is>
           <t>ネオプラ</t>
         </is>
       </c>
     </row>
     <row r="1155">
-      <c r="B1155" t="inlineStr">
+      <c r="B1155" s="0" t="inlineStr">
         <is>
           <t>LノイエギンエイデンGH</t>
         </is>
       </c>
-      <c r="C1155" t="inlineStr">
+      <c r="C1155" s="0" t="inlineStr">
         <is>
           <t>銀河英雄伝説</t>
         </is>
       </c>
     </row>
     <row r="1156">
-      <c r="B1156" t="inlineStr">
+      <c r="B1156" s="0" t="inlineStr">
         <is>
           <t>LバイオハザードRE:3 ZD</t>
         </is>
       </c>
-      <c r="C1156" t="inlineStr">
+      <c r="C1156" s="0" t="inlineStr">
         <is>
           <t>バイオRE:3</t>
         </is>
       </c>
     </row>
     <row r="1157">
-      <c r="B1157" t="inlineStr">
+      <c r="B1157" s="0" t="inlineStr">
         <is>
           <t>LバーニングエクスプレスZN</t>
         </is>
       </c>
-      <c r="C1157" t="inlineStr">
+      <c r="C1157" s="0" t="inlineStr">
         <is>
           <t>バーニングEXP.</t>
         </is>
       </c>
     </row>
     <row r="1158">
-      <c r="B1158" t="inlineStr">
+      <c r="B1158" s="0" t="inlineStr">
         <is>
           <t>LパチスロゴッドイーターリザレクションSLED</t>
         </is>
       </c>
-      <c r="C1158" t="inlineStr">
+      <c r="C1158" s="0" t="inlineStr">
         <is>
           <t>ゴッドイーター</t>
         </is>
       </c>
     </row>
     <row r="1159">
-      <c r="B1159" t="inlineStr">
+      <c r="B1159" s="0" t="inlineStr">
         <is>
           <t>Lパチスロスーパーリオエース2ND02H</t>
         </is>
       </c>
-      <c r="C1159" t="inlineStr">
+      <c r="C1159" s="0" t="inlineStr">
         <is>
           <t>リオエース2</t>
         </is>
       </c>
     </row>
     <row r="1160">
-      <c r="B1160" t="inlineStr">
+      <c r="B1160" s="0" t="inlineStr">
         <is>
           <t>Lパチスロ喰霊零Re/L3</t>
         </is>
       </c>
-      <c r="C1160" t="inlineStr">
+      <c r="C1160" s="0" t="inlineStr">
         <is>
           <t>喰霊零Re</t>
         </is>
       </c>
     </row>
     <row r="1161">
-      <c r="B1161" t="inlineStr">
+      <c r="B1161" s="0" t="inlineStr">
         <is>
           <t>Lマジカルハロウィン8FE</t>
         </is>
       </c>
-      <c r="C1161" t="inlineStr">
+      <c r="C1161" s="0" t="inlineStr">
         <is>
           <t>マジハロ8</t>
         </is>
       </c>
     </row>
     <row r="1162">
-      <c r="B1162" t="inlineStr">
+      <c r="B1162" s="0" t="inlineStr">
         <is>
           <t>Lモンキーターン5CE</t>
         </is>
       </c>
-      <c r="C1162" t="inlineStr">
+      <c r="C1162" s="0" t="inlineStr">
         <is>
           <t>モンキーターンV</t>
         </is>
       </c>
     </row>
     <row r="1163">
-      <c r="B1163" t="inlineStr">
+      <c r="B1163" s="0" t="inlineStr">
         <is>
           <t>LモンスターハンターライズXA</t>
         </is>
       </c>
-      <c r="C1163" t="inlineStr">
+      <c r="C1163" s="0" t="inlineStr">
         <is>
           <t>モンハンライズ</t>
         </is>
       </c>
     </row>
     <row r="1164">
-      <c r="B1164" t="inlineStr">
+      <c r="B1164" s="0" t="inlineStr">
         <is>
           <t>Lラブ嬢3M4</t>
         </is>
       </c>
-      <c r="C1164" t="inlineStr">
+      <c r="C1164" s="0" t="inlineStr">
         <is>
           <t>ラブ嬢3</t>
         </is>
       </c>
     </row>
     <row r="1165">
-      <c r="B1165" t="inlineStr">
+      <c r="B1165" s="0" t="inlineStr">
         <is>
           <t>Lレンタル彼女bK</t>
         </is>
       </c>
-      <c r="C1165" t="inlineStr">
+      <c r="C1165" s="0" t="inlineStr">
         <is>
           <t>かのかり</t>
         </is>
       </c>
     </row>
     <row r="1166">
-      <c r="B1166" t="inlineStr">
+      <c r="B1166" s="0" t="inlineStr">
         <is>
           <t>LレヴュースタァライトCX</t>
         </is>
       </c>
-      <c r="C1166" t="inlineStr">
+      <c r="C1166" s="0" t="inlineStr">
         <is>
           <t>スタァライト</t>
         </is>
       </c>
     </row>
     <row r="1167">
-      <c r="B1167" t="inlineStr">
+      <c r="B1167" s="0" t="inlineStr">
         <is>
           <t>L七つの魔剣が支配するPU</t>
         </is>
       </c>
-      <c r="C1167" t="inlineStr">
+      <c r="C1167" s="0" t="inlineStr">
         <is>
           <t>七つの魔剣</t>
         </is>
       </c>
     </row>
     <row r="1168">
-      <c r="B1168" t="inlineStr">
+      <c r="B1168" s="0" t="inlineStr">
         <is>
           <t>L南国育ちSPM1</t>
         </is>
       </c>
-      <c r="C1168" t="inlineStr">
+      <c r="C1168" s="0" t="inlineStr">
         <is>
           <t>南国育ちSPECIAL</t>
         </is>
       </c>
     </row>
     <row r="1169">
-      <c r="B1169" t="inlineStr">
+      <c r="B1169" s="0" t="inlineStr">
         <is>
           <t>L忍魂参 ~奥義皆伝ノ章~A3</t>
         </is>
       </c>
-      <c r="C1169" t="inlineStr">
+      <c r="C1169" s="0" t="inlineStr">
         <is>
           <t>忍魂参</t>
         </is>
       </c>
     </row>
     <row r="1170">
-      <c r="B1170" t="inlineStr">
+      <c r="B1170" s="0" t="inlineStr">
         <is>
           <t>L戦国コレクション6KS</t>
         </is>
       </c>
-      <c r="C1170" t="inlineStr">
+      <c r="C1170" s="0" t="inlineStr">
         <is>
           <t>戦コレ6</t>
         </is>
       </c>
     </row>
     <row r="1171">
-      <c r="B1171" t="inlineStr">
+      <c r="B1171" s="0" t="inlineStr">
         <is>
           <t>L戦国乙女5L8</t>
         </is>
       </c>
-      <c r="C1171" t="inlineStr">
+      <c r="C1171" s="0" t="inlineStr">
         <is>
           <t>戦国乙女5</t>
         </is>
       </c>
     </row>
     <row r="1172">
-      <c r="B1172" t="inlineStr">
+      <c r="B1172" s="0" t="inlineStr">
         <is>
           <t>L戦姫絶唱シンフォギア 正義の歌jA</t>
         </is>
       </c>
-      <c r="C1172" t="inlineStr">
+      <c r="C1172" s="0" t="inlineStr">
         <is>
           <t>シンフォギア正義</t>
         </is>
       </c>
     </row>
     <row r="1173">
-      <c r="B1173" t="inlineStr">
+      <c r="B1173" s="0" t="inlineStr">
         <is>
           <t>L東京喰種CT</t>
         </is>
       </c>
-      <c r="C1173" t="inlineStr">
+      <c r="C1173" s="0" t="inlineStr">
         <is>
           <t>東京喰種</t>
         </is>
       </c>
     </row>
     <row r="1174">
-      <c r="B1174" t="inlineStr">
+      <c r="B1174" s="0" t="inlineStr">
         <is>
           <t>L東京喰種FT</t>
         </is>
       </c>
-      <c r="C1174" t="inlineStr">
+      <c r="C1174" s="0" t="inlineStr">
         <is>
           <t>東京喰種</t>
         </is>
       </c>
     </row>
     <row r="1175">
-      <c r="B1175" t="inlineStr">
+      <c r="B1175" s="0" t="inlineStr">
         <is>
           <t>L機動戦士ガンダムユニコーン2jA</t>
         </is>
       </c>
-      <c r="C1175" t="inlineStr">
+      <c r="C1175" s="0" t="inlineStr">
         <is>
           <t>ユニコーン覚醒</t>
         </is>
       </c>
     </row>
     <row r="1176">
-      <c r="B1176" t="inlineStr">
+      <c r="B1176" s="0" t="inlineStr">
         <is>
           <t>L絶対衝激TK</t>
         </is>
       </c>
-      <c r="C1176" t="inlineStr">
+      <c r="C1176" s="0" t="inlineStr">
         <is>
           <t>L絶対衝激</t>
         </is>
       </c>
     </row>
     <row r="1177">
-      <c r="B1177" t="inlineStr">
+      <c r="B1177" s="0" t="inlineStr">
         <is>
           <t>L銭形5L2</t>
         </is>
       </c>
-      <c r="C1177" t="inlineStr">
+      <c r="C1177" s="0" t="inlineStr">
         <is>
           <t>主役は銭形5</t>
         </is>
       </c>
     </row>
     <row r="1178">
-      <c r="B1178" t="inlineStr">
+      <c r="B1178" s="0" t="inlineStr">
         <is>
           <t>L青春ブタ野郎L1</t>
         </is>
       </c>
-      <c r="C1178" t="inlineStr">
+      <c r="C1178" s="0" t="inlineStr">
         <is>
           <t>青ブタ</t>
         </is>
       </c>
     </row>
     <row r="1179">
-      <c r="B1179" t="inlineStr">
+      <c r="B1179" s="0" t="inlineStr">
         <is>
           <t>L麻雀物語S2</t>
         </is>
       </c>
-      <c r="C1179" t="inlineStr">
+      <c r="C1179" s="0" t="inlineStr">
         <is>
           <t>麻雀物語</t>
         </is>
       </c>
     </row>
     <row r="1180">
-      <c r="B1180" t="inlineStr">
+      <c r="B1180" s="0" t="inlineStr">
         <is>
           <t>S/クランキークレスト/CR</t>
         </is>
       </c>
-      <c r="C1180" t="inlineStr">
+      <c r="C1180" s="0" t="inlineStr">
         <is>
           <t>クランキークレスト</t>
         </is>
       </c>
     </row>
     <row r="1181">
-      <c r="B1181" t="inlineStr">
+      <c r="B1181" s="0" t="inlineStr">
         <is>
           <t>SジャグラーガールズSS-KH</t>
         </is>
       </c>
-      <c r="C1181" t="inlineStr">
+      <c r="C1181" s="0" t="inlineStr">
         <is>
           <t>ジャグラーガールズ</t>
         </is>
       </c>
     </row>
     <row r="1182">
-      <c r="B1182" t="inlineStr">
+      <c r="B1182" s="0" t="inlineStr">
         <is>
           <t>SネオアイムジャグラーEX-KK</t>
         </is>
       </c>
-      <c r="C1182" t="inlineStr">
+      <c r="C1182" s="0" t="inlineStr">
         <is>
           <t>ネオアイム</t>
         </is>
       </c>
     </row>
     <row r="1183">
-      <c r="B1183" t="inlineStr">
+      <c r="B1183" s="0" t="inlineStr">
         <is>
           <t>SミスタージャグラーKK</t>
         </is>
       </c>
-      <c r="C1183" t="inlineStr">
+      <c r="C1183" s="0" t="inlineStr">
         <is>
           <t>ミスジャグ</t>
+        </is>
+      </c>
+    </row>
+    <row r="1184">
+      <c r="B1184" t="inlineStr">
+        <is>
+          <t>ニューパルサーSPIII</t>
+        </is>
+      </c>
+      <c r="C1184" t="inlineStr">
+        <is>
+          <t>ニューパルSP3</t>
         </is>
       </c>
     </row>

--- a/機種名変換.xlsx
+++ b/機種名変換.xlsx
@@ -554,7 +554,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1184"/>
+  <dimension ref="A1:C1191"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
     <col width="8.796875" customWidth="1" style="1" min="1" max="1"/>
@@ -14752,14 +14752,98 @@
       </c>
     </row>
     <row r="1184">
-      <c r="B1184" t="inlineStr">
+      <c r="B1184" s="0" t="inlineStr">
         <is>
           <t>ニューパルサーSPIII</t>
         </is>
       </c>
-      <c r="C1184" t="inlineStr">
+      <c r="C1184" s="0" t="inlineStr">
         <is>
           <t>ニューパルSP3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1185">
+      <c r="B1185" t="inlineStr">
+        <is>
+          <t>沖ドキ!ゴージャス 25Φ</t>
+        </is>
+      </c>
+      <c r="C1185" t="inlineStr">
+        <is>
+          <t>沖ドキゴージャス25</t>
+        </is>
+      </c>
+    </row>
+    <row r="1186">
+      <c r="B1186" t="inlineStr">
+        <is>
+          <t>スマスロ ようこそ実力至上主義の教室へ</t>
+        </is>
+      </c>
+      <c r="C1186" t="inlineStr">
+        <is>
+          <t>よう実</t>
+        </is>
+      </c>
+    </row>
+    <row r="1187">
+      <c r="B1187" t="inlineStr">
+        <is>
+          <t>L 絶対衝激〜PLATONIC HEART〜</t>
+        </is>
+      </c>
+      <c r="C1187" t="inlineStr">
+        <is>
+          <t>L絶対衝激</t>
+        </is>
+      </c>
+    </row>
+    <row r="1188">
+      <c r="B1188" t="inlineStr">
+        <is>
+          <t>スマスロ 緑ドン VIVA!情熱南米編 REVIVAL</t>
+        </is>
+      </c>
+      <c r="C1188" t="inlineStr">
+        <is>
+          <t>緑ドン</t>
+        </is>
+      </c>
+    </row>
+    <row r="1189">
+      <c r="B1189" t="inlineStr">
+        <is>
+          <t>LBエヴァンゲリオンsR</t>
+        </is>
+      </c>
+      <c r="C1189" t="inlineStr">
+        <is>
+          <t>ヱヴァ約束</t>
+        </is>
+      </c>
+    </row>
+    <row r="1190">
+      <c r="B1190" t="inlineStr">
+        <is>
+          <t>S/沖ドキ!BLACK/GS</t>
+        </is>
+      </c>
+      <c r="C1190" t="inlineStr">
+        <is>
+          <t>沖ドキBLACK</t>
+        </is>
+      </c>
+    </row>
+    <row r="1191">
+      <c r="B1191" t="inlineStr">
+        <is>
+          <t>LToLOVEるダークネスS6</t>
+        </is>
+      </c>
+      <c r="C1191" t="inlineStr">
+        <is>
+          <t>ToLOVEる</t>
         </is>
       </c>
     </row>

--- a/機種名変換.xlsx
+++ b/機種名変換.xlsx
@@ -554,7 +554,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1193"/>
+  <dimension ref="A1:C1195"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
     <col width="8.796875" customWidth="1" style="1" min="1" max="1"/>
@@ -14848,26 +14848,50 @@
       </c>
     </row>
     <row r="1192">
-      <c r="B1192" t="inlineStr">
+      <c r="B1192" s="0" t="inlineStr">
         <is>
           <t>Lモンスターハンターライズ:サンブレイク</t>
         </is>
       </c>
-      <c r="C1192" t="inlineStr">
+      <c r="C1192" s="0" t="inlineStr">
         <is>
           <t>モンハンサンブレイク</t>
         </is>
       </c>
     </row>
     <row r="1193">
-      <c r="B1193" t="inlineStr">
+      <c r="B1193" s="0" t="inlineStr">
         <is>
           <t>L獣王</t>
         </is>
       </c>
-      <c r="C1193" t="inlineStr">
+      <c r="C1193" s="0" t="inlineStr">
         <is>
           <t>獣王</t>
+        </is>
+      </c>
+    </row>
+    <row r="1194">
+      <c r="B1194" t="inlineStr">
+        <is>
+          <t>マイジャグラーVI</t>
+        </is>
+      </c>
+      <c r="C1194" t="inlineStr">
+        <is>
+          <t>マイジャグVI</t>
+        </is>
+      </c>
+    </row>
+    <row r="1195">
+      <c r="B1195" t="inlineStr">
+        <is>
+          <t>Lパリピ孔明</t>
+        </is>
+      </c>
+      <c r="C1195" t="inlineStr">
+        <is>
+          <t>パリピ孔明</t>
         </is>
       </c>
     </row>

--- a/機種名変換.xlsx
+++ b/機種名変換.xlsx
@@ -554,7 +554,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1195"/>
+  <dimension ref="A1:C1196"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
     <col width="8.796875" customWidth="1" style="1" min="1" max="1"/>
@@ -14872,26 +14872,38 @@
       </c>
     </row>
     <row r="1194">
-      <c r="B1194" t="inlineStr">
+      <c r="B1194" s="0" t="inlineStr">
         <is>
           <t>マイジャグラーVI</t>
         </is>
       </c>
-      <c r="C1194" t="inlineStr">
+      <c r="C1194" s="0" t="inlineStr">
         <is>
           <t>マイジャグVI</t>
         </is>
       </c>
     </row>
     <row r="1195">
-      <c r="B1195" t="inlineStr">
+      <c r="B1195" s="0" t="inlineStr">
         <is>
           <t>Lパリピ孔明</t>
         </is>
       </c>
-      <c r="C1195" t="inlineStr">
+      <c r="C1195" s="0" t="inlineStr">
         <is>
           <t>パリピ孔明</t>
+        </is>
+      </c>
+    </row>
+    <row r="1196">
+      <c r="B1196" t="inlineStr">
+        <is>
+          <t>L転生王女と天才令嬢の魔</t>
+        </is>
+      </c>
+      <c r="C1196" t="inlineStr">
+        <is>
+          <t>転生王女と天才令嬢</t>
         </is>
       </c>
     </row>

--- a/機種名変換.xlsx
+++ b/機種名変換.xlsx
@@ -554,7 +554,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1196"/>
+  <dimension ref="A1:C1198"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
     <col width="8.796875" customWidth="1" style="1" min="1" max="1"/>
@@ -14896,14 +14896,38 @@
       </c>
     </row>
     <row r="1196">
-      <c r="B1196" t="inlineStr">
+      <c r="B1196" s="0" t="inlineStr">
         <is>
           <t>L転生王女と天才令嬢の魔</t>
         </is>
       </c>
-      <c r="C1196" t="inlineStr">
+      <c r="C1196" s="0" t="inlineStr">
         <is>
           <t>転生王女と天才令嬢</t>
+        </is>
+      </c>
+    </row>
+    <row r="1197">
+      <c r="B1197" t="inlineStr">
+        <is>
+          <t>スマスロ モンスターハンターライズ:サンブレイク</t>
+        </is>
+      </c>
+      <c r="C1197" t="inlineStr">
+        <is>
+          <t>モンハンサンブレイク</t>
+        </is>
+      </c>
+    </row>
+    <row r="1198">
+      <c r="B1198" t="inlineStr">
+        <is>
+          <t>スマスロ 獣王</t>
+        </is>
+      </c>
+      <c r="C1198" t="inlineStr">
+        <is>
+          <t>獣王</t>
         </is>
       </c>
     </row>

--- a/機種名変換.xlsx
+++ b/機種名変換.xlsx
@@ -554,7 +554,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1198"/>
+  <dimension ref="A1:C1199"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
     <col width="8.796875" customWidth="1" style="1" min="1" max="1"/>
@@ -14908,26 +14908,38 @@
       </c>
     </row>
     <row r="1197">
-      <c r="B1197" t="inlineStr">
+      <c r="B1197" s="0" t="inlineStr">
         <is>
           <t>スマスロ モンスターハンターライズ:サンブレイク</t>
         </is>
       </c>
-      <c r="C1197" t="inlineStr">
+      <c r="C1197" s="0" t="inlineStr">
         <is>
           <t>モンハンサンブレイク</t>
         </is>
       </c>
     </row>
     <row r="1198">
-      <c r="B1198" t="inlineStr">
+      <c r="B1198" s="0" t="inlineStr">
         <is>
           <t>スマスロ 獣王</t>
         </is>
       </c>
-      <c r="C1198" t="inlineStr">
+      <c r="C1198" s="0" t="inlineStr">
         <is>
           <t>獣王</t>
+        </is>
+      </c>
+    </row>
+    <row r="1199">
+      <c r="B1199" t="inlineStr">
+        <is>
+          <t>スマスロパリピ孔明</t>
+        </is>
+      </c>
+      <c r="C1199" t="inlineStr">
+        <is>
+          <t>パリピ孔明</t>
         </is>
       </c>
     </row>

--- a/機種名変換.xlsx
+++ b/機種名変換.xlsx
@@ -554,7 +554,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1199"/>
+  <dimension ref="A1:C1200"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
     <col width="8.796875" customWidth="1" style="1" min="1" max="1"/>
@@ -14932,14 +14932,26 @@
       </c>
     </row>
     <row r="1199">
-      <c r="B1199" t="inlineStr">
+      <c r="B1199" s="0" t="inlineStr">
         <is>
           <t>スマスロパリピ孔明</t>
         </is>
       </c>
-      <c r="C1199" t="inlineStr">
+      <c r="C1199" s="0" t="inlineStr">
         <is>
           <t>パリピ孔明</t>
+        </is>
+      </c>
+    </row>
+    <row r="1200">
+      <c r="B1200" t="inlineStr">
+        <is>
+          <t>L転生王女と天才令嬢の魔法革命</t>
+        </is>
+      </c>
+      <c r="C1200" t="inlineStr">
+        <is>
+          <t>転生王女と天才令嬢</t>
         </is>
       </c>
     </row>

--- a/機種名変換.xlsx
+++ b/機種名変換.xlsx
@@ -554,7 +554,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1200"/>
+  <dimension ref="A1:C1201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
     <col width="8.796875" customWidth="1" style="1" min="1" max="1"/>
@@ -14944,14 +14944,26 @@
       </c>
     </row>
     <row r="1200">
-      <c r="B1200" t="inlineStr">
+      <c r="B1200" s="0" t="inlineStr">
         <is>
           <t>L転生王女と天才令嬢の魔法革命</t>
         </is>
       </c>
-      <c r="C1200" t="inlineStr">
+      <c r="C1200" s="0" t="inlineStr">
         <is>
           <t>転生王女と天才令嬢</t>
+        </is>
+      </c>
+    </row>
+    <row r="1201">
+      <c r="B1201" t="inlineStr">
+        <is>
+          <t>L MHRサンブレイクXA</t>
+        </is>
+      </c>
+      <c r="C1201" t="inlineStr">
+        <is>
+          <t>モンハンサンブレイク</t>
         </is>
       </c>
     </row>

--- a/機種名変換.xlsx
+++ b/機種名変換.xlsx
@@ -554,7 +554,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1201"/>
+  <dimension ref="A1:C1202"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
     <col width="8.796875" customWidth="1" style="1" min="1" max="1"/>
@@ -14956,14 +14956,26 @@
       </c>
     </row>
     <row r="1201">
-      <c r="B1201" t="inlineStr">
+      <c r="B1201" s="0" t="inlineStr">
         <is>
           <t>L MHRサンブレイクXA</t>
         </is>
       </c>
-      <c r="C1201" t="inlineStr">
+      <c r="C1201" s="0" t="inlineStr">
         <is>
           <t>モンハンサンブレイク</t>
+        </is>
+      </c>
+    </row>
+    <row r="1202">
+      <c r="B1202" t="inlineStr">
+        <is>
+          <t>SLOTドルアーガの塔</t>
+        </is>
+      </c>
+      <c r="C1202" t="inlineStr">
+        <is>
+          <t>ドルアーガの塔</t>
         </is>
       </c>
     </row>

--- a/機種名変換.xlsx
+++ b/機種名変換.xlsx
@@ -554,7 +554,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1202"/>
+  <dimension ref="A1:C1204"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
     <col width="8.796875" customWidth="1" style="1" min="1" max="1"/>
@@ -14968,14 +14968,38 @@
       </c>
     </row>
     <row r="1202">
-      <c r="B1202" t="inlineStr">
+      <c r="B1202" s="0" t="inlineStr">
         <is>
           <t>SLOTドルアーガの塔</t>
         </is>
       </c>
-      <c r="C1202" t="inlineStr">
+      <c r="C1202" s="0" t="inlineStr">
         <is>
           <t>ドルアーガの塔</t>
+        </is>
+      </c>
+    </row>
+    <row r="1203">
+      <c r="B1203" t="inlineStr">
+        <is>
+          <t>L転天</t>
+        </is>
+      </c>
+      <c r="C1203" t="inlineStr">
+        <is>
+          <t>転生王女と天才令嬢</t>
+        </is>
+      </c>
+    </row>
+    <row r="1204">
+      <c r="B1204" t="inlineStr">
+        <is>
+          <t>主役は銭形4</t>
+        </is>
+      </c>
+      <c r="C1204" t="inlineStr">
+        <is>
+          <t>主役は銭形4</t>
         </is>
       </c>
     </row>

--- a/機種名変換.xlsx
+++ b/機種名変換.xlsx
@@ -554,7 +554,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1204"/>
+  <dimension ref="A1:C1206"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
     <col width="8.796875" customWidth="1" style="1" min="1" max="1"/>
@@ -14980,26 +14980,50 @@
       </c>
     </row>
     <row r="1203">
-      <c r="B1203" t="inlineStr">
+      <c r="B1203" s="0" t="inlineStr">
         <is>
           <t>L転天</t>
         </is>
       </c>
-      <c r="C1203" t="inlineStr">
+      <c r="C1203" s="0" t="inlineStr">
         <is>
           <t>転生王女と天才令嬢</t>
         </is>
       </c>
     </row>
     <row r="1204">
-      <c r="B1204" t="inlineStr">
+      <c r="B1204" s="0" t="inlineStr">
         <is>
           <t>主役は銭形4</t>
         </is>
       </c>
-      <c r="C1204" t="inlineStr">
+      <c r="C1204" s="0" t="inlineStr">
         <is>
           <t>主役は銭形4</t>
+        </is>
+      </c>
+    </row>
+    <row r="1205">
+      <c r="B1205" t="inlineStr">
+        <is>
+          <t>Lノイエ銀英伝</t>
+        </is>
+      </c>
+      <c r="C1205" t="inlineStr">
+        <is>
+          <t>銀河英雄伝説</t>
+        </is>
+      </c>
+    </row>
+    <row r="1206">
+      <c r="B1206" t="inlineStr">
+        <is>
+          <t>沖ドキ!ゴージャス25</t>
+        </is>
+      </c>
+      <c r="C1206" t="inlineStr">
+        <is>
+          <t>沖ドキゴージャス25</t>
         </is>
       </c>
     </row>

--- a/機種名変換.xlsx
+++ b/機種名変換.xlsx
@@ -554,7 +554,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1206"/>
+  <dimension ref="A1:C1209"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
     <col width="8.796875" customWidth="1" style="1" min="1" max="1"/>
@@ -15004,26 +15004,62 @@
       </c>
     </row>
     <row r="1205">
-      <c r="B1205" t="inlineStr">
+      <c r="B1205" s="0" t="inlineStr">
         <is>
           <t>Lノイエ銀英伝</t>
         </is>
       </c>
-      <c r="C1205" t="inlineStr">
+      <c r="C1205" s="0" t="inlineStr">
         <is>
           <t>銀河英雄伝説</t>
         </is>
       </c>
     </row>
     <row r="1206">
-      <c r="B1206" t="inlineStr">
+      <c r="B1206" s="0" t="inlineStr">
         <is>
           <t>沖ドキ!ゴージャス25</t>
         </is>
       </c>
-      <c r="C1206" t="inlineStr">
+      <c r="C1206" s="0" t="inlineStr">
         <is>
           <t>沖ドキゴージャス25</t>
+        </is>
+      </c>
+    </row>
+    <row r="1207">
+      <c r="B1207" t="inlineStr">
+        <is>
+          <t>L 獣王 XZ</t>
+        </is>
+      </c>
+      <c r="C1207" t="inlineStr">
+        <is>
+          <t>獣王</t>
+        </is>
+      </c>
+    </row>
+    <row r="1208">
+      <c r="B1208" t="inlineStr">
+        <is>
+          <t>Lパチスロパリピ孔明YE05H</t>
+        </is>
+      </c>
+      <c r="C1208" t="inlineStr">
+        <is>
+          <t>パリピ孔明</t>
+        </is>
+      </c>
+    </row>
+    <row r="1209">
+      <c r="B1209" t="inlineStr">
+        <is>
+          <t>SマイジャグラーVIKK</t>
+        </is>
+      </c>
+      <c r="C1209" t="inlineStr">
+        <is>
+          <t>マイジャグVI</t>
         </is>
       </c>
     </row>

--- a/機種名変換.xlsx
+++ b/機種名変換.xlsx
@@ -554,7 +554,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1209"/>
+  <dimension ref="A1:C1240"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
     <col width="8.796875" customWidth="1" style="1" min="1" max="1"/>
@@ -15028,38 +15028,410 @@
       </c>
     </row>
     <row r="1207">
-      <c r="B1207" t="inlineStr">
+      <c r="B1207" s="0" t="inlineStr">
         <is>
           <t>L 獣王 XZ</t>
         </is>
       </c>
-      <c r="C1207" t="inlineStr">
+      <c r="C1207" s="0" t="inlineStr">
         <is>
           <t>獣王</t>
         </is>
       </c>
     </row>
     <row r="1208">
-      <c r="B1208" t="inlineStr">
+      <c r="B1208" s="0" t="inlineStr">
         <is>
           <t>Lパチスロパリピ孔明YE05H</t>
         </is>
       </c>
-      <c r="C1208" t="inlineStr">
+      <c r="C1208" s="0" t="inlineStr">
         <is>
           <t>パリピ孔明</t>
         </is>
       </c>
     </row>
     <row r="1209">
-      <c r="B1209" t="inlineStr">
+      <c r="B1209" s="0" t="inlineStr">
         <is>
           <t>SマイジャグラーVIKK</t>
         </is>
       </c>
-      <c r="C1209" t="inlineStr">
+      <c r="C1209" s="0" t="inlineStr">
         <is>
           <t>マイジャグVI</t>
+        </is>
+      </c>
+    </row>
+    <row r="1210">
+      <c r="B1210" t="inlineStr">
+        <is>
+          <t>A‐SLOT+ 異世界かるてっと</t>
+        </is>
+      </c>
+      <c r="C1210" t="inlineStr">
+        <is>
+          <t>異世界かるてっと</t>
+        </is>
+      </c>
+    </row>
+    <row r="1211">
+      <c r="B1211" t="inlineStr">
+        <is>
+          <t>ToLOVEるダークネス TRANCE ver.8.7</t>
+        </is>
+      </c>
+      <c r="C1211" t="inlineStr">
+        <is>
+          <t>ToLOVEるトランス</t>
+        </is>
+      </c>
+    </row>
+    <row r="1212">
+      <c r="B1212" t="inlineStr">
+        <is>
+          <t>うみねこのなく頃に2</t>
+        </is>
+      </c>
+      <c r="C1212" t="inlineStr">
+        <is>
+          <t>うみねこ2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1213">
+      <c r="B1213" t="inlineStr">
+        <is>
+          <t>かぐや様は告らせたい</t>
+        </is>
+      </c>
+      <c r="C1213" t="inlineStr">
+        <is>
+          <t>かぐや様</t>
+        </is>
+      </c>
+    </row>
+    <row r="1214">
+      <c r="B1214" t="inlineStr">
+        <is>
+          <t>からくりサーカス2</t>
+        </is>
+      </c>
+      <c r="C1214" t="inlineStr">
+        <is>
+          <t>からくりサーカス2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1215">
+      <c r="B1215" t="inlineStr">
+        <is>
+          <t>とある魔術の禁書目録2</t>
+        </is>
+      </c>
+      <c r="C1215" t="inlineStr">
+        <is>
+          <t>とある禁書目録2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1216">
+      <c r="B1216" t="inlineStr">
+        <is>
+          <t>やじきた道中記参る!</t>
+        </is>
+      </c>
+      <c r="C1216" t="inlineStr">
+        <is>
+          <t>やじきた</t>
+        </is>
+      </c>
+    </row>
+    <row r="1217">
+      <c r="B1217" t="inlineStr">
+        <is>
+          <t>アズールレーン THE ANIMATION</t>
+        </is>
+      </c>
+      <c r="C1217" t="inlineStr">
+        <is>
+          <t>アズールレーン</t>
+        </is>
+      </c>
+    </row>
+    <row r="1218">
+      <c r="B1218" t="inlineStr">
+        <is>
+          <t>スマスロ炎炎ノ消防隊2</t>
+        </is>
+      </c>
+      <c r="C1218" t="inlineStr">
+        <is>
+          <t>炎炎ノ消防隊2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1219">
+      <c r="B1219" t="inlineStr">
+        <is>
+          <t>スーパーブラックジャック</t>
+        </is>
+      </c>
+      <c r="C1219" t="inlineStr">
+        <is>
+          <t>スーパーBJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="1220">
+      <c r="B1220" t="inlineStr">
+        <is>
+          <t>ディスクアップ ULTRAREMIX</t>
+        </is>
+      </c>
+      <c r="C1220" t="inlineStr">
+        <is>
+          <t>ディスクアップUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="1221">
+      <c r="B1221" t="inlineStr">
+        <is>
+          <t>ネオプラネット</t>
+        </is>
+      </c>
+      <c r="C1221" t="inlineStr">
+        <is>
+          <t>ネオプラ</t>
+        </is>
+      </c>
+    </row>
+    <row r="1222">
+      <c r="B1222" t="inlineStr">
+        <is>
+          <t>バンドリ!</t>
+        </is>
+      </c>
+      <c r="C1222" t="inlineStr">
+        <is>
+          <t>バンドリ</t>
+        </is>
+      </c>
+    </row>
+    <row r="1223">
+      <c r="B1223" t="inlineStr">
+        <is>
+          <t>パリピ孔明</t>
+        </is>
+      </c>
+      <c r="C1223" t="inlineStr">
+        <is>
+          <t>パリピ孔明</t>
+        </is>
+      </c>
+    </row>
+    <row r="1224">
+      <c r="B1224" t="inlineStr">
+        <is>
+          <t>マギアレコード 魔法少女まどか☆マギカ外伝</t>
+        </is>
+      </c>
+      <c r="C1224" t="inlineStr">
+        <is>
+          <t>マギレコ</t>
+        </is>
+      </c>
+    </row>
+    <row r="1225">
+      <c r="B1225" t="inlineStr">
+        <is>
+          <t>ミリオンゴッド‐神々の軌跡‐</t>
+        </is>
+      </c>
+      <c r="C1225" t="inlineStr">
+        <is>
+          <t>ゴッド神々の軌跡</t>
+        </is>
+      </c>
+    </row>
+    <row r="1226">
+      <c r="B1226" t="inlineStr">
+        <is>
+          <t>モンスターハンターライズ</t>
+        </is>
+      </c>
+      <c r="C1226" t="inlineStr">
+        <is>
+          <t>モンハンライズ</t>
+        </is>
+      </c>
+    </row>
+    <row r="1227">
+      <c r="B1227" t="inlineStr">
+        <is>
+          <t>モンスターハンターライズ:サンブレイク</t>
+        </is>
+      </c>
+      <c r="C1227" t="inlineStr">
+        <is>
+          <t>モンハンサンブレイク</t>
+        </is>
+      </c>
+    </row>
+    <row r="1228">
+      <c r="B1228" t="inlineStr">
+        <is>
+          <t>リコリス・リコイル</t>
+        </is>
+      </c>
+      <c r="C1228" t="inlineStr">
+        <is>
+          <t>リコリス</t>
+        </is>
+      </c>
+    </row>
+    <row r="1229">
+      <c r="B1229" t="inlineStr">
+        <is>
+          <t>化物語</t>
+        </is>
+      </c>
+      <c r="C1229" t="inlineStr">
+        <is>
+          <t>スマスロ化物語</t>
+        </is>
+      </c>
+    </row>
+    <row r="1230">
+      <c r="B1230" t="inlineStr">
+        <is>
+          <t>北斗の拳 転生の章2</t>
+        </is>
+      </c>
+      <c r="C1230" t="inlineStr">
+        <is>
+          <t>北斗転生2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1231">
+      <c r="B1231" t="inlineStr">
+        <is>
+          <t>喰霊‐零‐Re</t>
+        </is>
+      </c>
+      <c r="C1231" t="inlineStr">
+        <is>
+          <t>喰霊零Re</t>
+        </is>
+      </c>
+    </row>
+    <row r="1232">
+      <c r="B1232" t="inlineStr">
+        <is>
+          <t>彼女、お借りします</t>
+        </is>
+      </c>
+      <c r="C1232" t="inlineStr">
+        <is>
+          <t>かのかり</t>
+        </is>
+      </c>
+    </row>
+    <row r="1233">
+      <c r="B1233" t="inlineStr">
+        <is>
+          <t>戦国乙女5 業火を穿つ宿焔の双刃</t>
+        </is>
+      </c>
+      <c r="C1233" t="inlineStr">
+        <is>
+          <t>戦国乙女5</t>
+        </is>
+      </c>
+    </row>
+    <row r="1234">
+      <c r="B1234" t="inlineStr">
+        <is>
+          <t>攻殻機動隊</t>
+        </is>
+      </c>
+      <c r="C1234" t="inlineStr">
+        <is>
+          <t>L攻殻機動隊</t>
+        </is>
+      </c>
+    </row>
+    <row r="1235">
+      <c r="B1235" t="inlineStr">
+        <is>
+          <t>新鬼武者3</t>
+        </is>
+      </c>
+      <c r="C1235" t="inlineStr">
+        <is>
+          <t>新鬼武者3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1236">
+      <c r="B1236" t="inlineStr">
+        <is>
+          <t>獣王</t>
+        </is>
+      </c>
+      <c r="C1236" t="inlineStr">
+        <is>
+          <t>獣王</t>
+        </is>
+      </c>
+    </row>
+    <row r="1237">
+      <c r="B1237" t="inlineStr">
+        <is>
+          <t>甲鉄城のカバネリ 海門(うなと)決戦</t>
+        </is>
+      </c>
+      <c r="C1237" t="inlineStr">
+        <is>
+          <t>カバネリ海門決戦</t>
+        </is>
+      </c>
+    </row>
+    <row r="1238">
+      <c r="B1238" t="inlineStr">
+        <is>
+          <t>痛いのは嫌なので防御力に極振りしたいと思います。</t>
+        </is>
+      </c>
+      <c r="C1238" t="inlineStr">
+        <is>
+          <t>防振り</t>
+        </is>
+      </c>
+    </row>
+    <row r="1239">
+      <c r="B1239" t="inlineStr">
+        <is>
+          <t>青春ブタ野郎はバニーガール先輩の夢を見ない</t>
+        </is>
+      </c>
+      <c r="C1239" t="inlineStr">
+        <is>
+          <t>青ブタ</t>
+        </is>
+      </c>
+    </row>
+    <row r="1240">
+      <c r="B1240" t="inlineStr">
+        <is>
+          <t>革命機ヴァルヴレイヴ2</t>
+        </is>
+      </c>
+      <c r="C1240" t="inlineStr">
+        <is>
+          <t>ヴァルヴレイヴ2</t>
         </is>
       </c>
     </row>

--- a/機種名変換.xlsx
+++ b/機種名変換.xlsx
@@ -554,7 +554,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1240"/>
+  <dimension ref="A1:C1241"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
     <col width="8.796875" customWidth="1" style="1" min="1" max="1"/>
@@ -15064,374 +15064,386 @@
       </c>
     </row>
     <row r="1210">
-      <c r="B1210" t="inlineStr">
+      <c r="B1210" s="0" t="inlineStr">
         <is>
           <t>A‐SLOT+ 異世界かるてっと</t>
         </is>
       </c>
-      <c r="C1210" t="inlineStr">
+      <c r="C1210" s="0" t="inlineStr">
         <is>
           <t>異世界かるてっと</t>
         </is>
       </c>
     </row>
     <row r="1211">
-      <c r="B1211" t="inlineStr">
+      <c r="B1211" s="0" t="inlineStr">
         <is>
           <t>ToLOVEるダークネス TRANCE ver.8.7</t>
         </is>
       </c>
-      <c r="C1211" t="inlineStr">
+      <c r="C1211" s="0" t="inlineStr">
         <is>
           <t>ToLOVEるトランス</t>
         </is>
       </c>
     </row>
     <row r="1212">
-      <c r="B1212" t="inlineStr">
+      <c r="B1212" s="0" t="inlineStr">
         <is>
           <t>うみねこのなく頃に2</t>
         </is>
       </c>
-      <c r="C1212" t="inlineStr">
+      <c r="C1212" s="0" t="inlineStr">
         <is>
           <t>うみねこ2</t>
         </is>
       </c>
     </row>
     <row r="1213">
-      <c r="B1213" t="inlineStr">
+      <c r="B1213" s="0" t="inlineStr">
         <is>
           <t>かぐや様は告らせたい</t>
         </is>
       </c>
-      <c r="C1213" t="inlineStr">
+      <c r="C1213" s="0" t="inlineStr">
         <is>
           <t>かぐや様</t>
         </is>
       </c>
     </row>
     <row r="1214">
-      <c r="B1214" t="inlineStr">
+      <c r="B1214" s="0" t="inlineStr">
         <is>
           <t>からくりサーカス2</t>
         </is>
       </c>
-      <c r="C1214" t="inlineStr">
+      <c r="C1214" s="0" t="inlineStr">
         <is>
           <t>からくりサーカス2</t>
         </is>
       </c>
     </row>
     <row r="1215">
-      <c r="B1215" t="inlineStr">
+      <c r="B1215" s="0" t="inlineStr">
         <is>
           <t>とある魔術の禁書目録2</t>
         </is>
       </c>
-      <c r="C1215" t="inlineStr">
+      <c r="C1215" s="0" t="inlineStr">
         <is>
           <t>とある禁書目録2</t>
         </is>
       </c>
     </row>
     <row r="1216">
-      <c r="B1216" t="inlineStr">
+      <c r="B1216" s="0" t="inlineStr">
         <is>
           <t>やじきた道中記参る!</t>
         </is>
       </c>
-      <c r="C1216" t="inlineStr">
+      <c r="C1216" s="0" t="inlineStr">
         <is>
           <t>やじきた</t>
         </is>
       </c>
     </row>
     <row r="1217">
-      <c r="B1217" t="inlineStr">
+      <c r="B1217" s="0" t="inlineStr">
         <is>
           <t>アズールレーン THE ANIMATION</t>
         </is>
       </c>
-      <c r="C1217" t="inlineStr">
+      <c r="C1217" s="0" t="inlineStr">
         <is>
           <t>アズールレーン</t>
         </is>
       </c>
     </row>
     <row r="1218">
-      <c r="B1218" t="inlineStr">
+      <c r="B1218" s="0" t="inlineStr">
         <is>
           <t>スマスロ炎炎ノ消防隊2</t>
         </is>
       </c>
-      <c r="C1218" t="inlineStr">
+      <c r="C1218" s="0" t="inlineStr">
         <is>
           <t>炎炎ノ消防隊2</t>
         </is>
       </c>
     </row>
     <row r="1219">
-      <c r="B1219" t="inlineStr">
+      <c r="B1219" s="0" t="inlineStr">
         <is>
           <t>スーパーブラックジャック</t>
         </is>
       </c>
-      <c r="C1219" t="inlineStr">
+      <c r="C1219" s="0" t="inlineStr">
         <is>
           <t>スーパーBJ</t>
         </is>
       </c>
     </row>
     <row r="1220">
-      <c r="B1220" t="inlineStr">
+      <c r="B1220" s="0" t="inlineStr">
         <is>
           <t>ディスクアップ ULTRAREMIX</t>
         </is>
       </c>
-      <c r="C1220" t="inlineStr">
+      <c r="C1220" s="0" t="inlineStr">
         <is>
           <t>ディスクアップUR</t>
         </is>
       </c>
     </row>
     <row r="1221">
-      <c r="B1221" t="inlineStr">
+      <c r="B1221" s="0" t="inlineStr">
         <is>
           <t>ネオプラネット</t>
         </is>
       </c>
-      <c r="C1221" t="inlineStr">
+      <c r="C1221" s="0" t="inlineStr">
         <is>
           <t>ネオプラ</t>
         </is>
       </c>
     </row>
     <row r="1222">
-      <c r="B1222" t="inlineStr">
+      <c r="B1222" s="0" t="inlineStr">
         <is>
           <t>バンドリ!</t>
         </is>
       </c>
-      <c r="C1222" t="inlineStr">
+      <c r="C1222" s="0" t="inlineStr">
         <is>
           <t>バンドリ</t>
         </is>
       </c>
     </row>
     <row r="1223">
-      <c r="B1223" t="inlineStr">
+      <c r="B1223" s="0" t="inlineStr">
         <is>
           <t>パリピ孔明</t>
         </is>
       </c>
-      <c r="C1223" t="inlineStr">
+      <c r="C1223" s="0" t="inlineStr">
         <is>
           <t>パリピ孔明</t>
         </is>
       </c>
     </row>
     <row r="1224">
-      <c r="B1224" t="inlineStr">
+      <c r="B1224" s="0" t="inlineStr">
         <is>
           <t>マギアレコード 魔法少女まどか☆マギカ外伝</t>
         </is>
       </c>
-      <c r="C1224" t="inlineStr">
+      <c r="C1224" s="0" t="inlineStr">
         <is>
           <t>マギレコ</t>
         </is>
       </c>
     </row>
     <row r="1225">
-      <c r="B1225" t="inlineStr">
+      <c r="B1225" s="0" t="inlineStr">
         <is>
           <t>ミリオンゴッド‐神々の軌跡‐</t>
         </is>
       </c>
-      <c r="C1225" t="inlineStr">
+      <c r="C1225" s="0" t="inlineStr">
         <is>
           <t>ゴッド神々の軌跡</t>
         </is>
       </c>
     </row>
     <row r="1226">
-      <c r="B1226" t="inlineStr">
+      <c r="B1226" s="0" t="inlineStr">
         <is>
           <t>モンスターハンターライズ</t>
         </is>
       </c>
-      <c r="C1226" t="inlineStr">
+      <c r="C1226" s="0" t="inlineStr">
         <is>
           <t>モンハンライズ</t>
         </is>
       </c>
     </row>
     <row r="1227">
-      <c r="B1227" t="inlineStr">
+      <c r="B1227" s="0" t="inlineStr">
         <is>
           <t>モンスターハンターライズ:サンブレイク</t>
         </is>
       </c>
-      <c r="C1227" t="inlineStr">
+      <c r="C1227" s="0" t="inlineStr">
         <is>
           <t>モンハンサンブレイク</t>
         </is>
       </c>
     </row>
     <row r="1228">
-      <c r="B1228" t="inlineStr">
+      <c r="B1228" s="0" t="inlineStr">
         <is>
           <t>リコリス・リコイル</t>
         </is>
       </c>
-      <c r="C1228" t="inlineStr">
+      <c r="C1228" s="0" t="inlineStr">
         <is>
           <t>リコリス</t>
         </is>
       </c>
     </row>
     <row r="1229">
-      <c r="B1229" t="inlineStr">
+      <c r="B1229" s="0" t="inlineStr">
         <is>
           <t>化物語</t>
         </is>
       </c>
-      <c r="C1229" t="inlineStr">
+      <c r="C1229" s="0" t="inlineStr">
         <is>
           <t>スマスロ化物語</t>
         </is>
       </c>
     </row>
     <row r="1230">
-      <c r="B1230" t="inlineStr">
+      <c r="B1230" s="0" t="inlineStr">
         <is>
           <t>北斗の拳 転生の章2</t>
         </is>
       </c>
-      <c r="C1230" t="inlineStr">
+      <c r="C1230" s="0" t="inlineStr">
         <is>
           <t>北斗転生2</t>
         </is>
       </c>
     </row>
     <row r="1231">
-      <c r="B1231" t="inlineStr">
+      <c r="B1231" s="0" t="inlineStr">
         <is>
           <t>喰霊‐零‐Re</t>
         </is>
       </c>
-      <c r="C1231" t="inlineStr">
+      <c r="C1231" s="0" t="inlineStr">
         <is>
           <t>喰霊零Re</t>
         </is>
       </c>
     </row>
     <row r="1232">
-      <c r="B1232" t="inlineStr">
+      <c r="B1232" s="0" t="inlineStr">
         <is>
           <t>彼女、お借りします</t>
         </is>
       </c>
-      <c r="C1232" t="inlineStr">
+      <c r="C1232" s="0" t="inlineStr">
         <is>
           <t>かのかり</t>
         </is>
       </c>
     </row>
     <row r="1233">
-      <c r="B1233" t="inlineStr">
+      <c r="B1233" s="0" t="inlineStr">
         <is>
           <t>戦国乙女5 業火を穿つ宿焔の双刃</t>
         </is>
       </c>
-      <c r="C1233" t="inlineStr">
+      <c r="C1233" s="0" t="inlineStr">
         <is>
           <t>戦国乙女5</t>
         </is>
       </c>
     </row>
     <row r="1234">
-      <c r="B1234" t="inlineStr">
+      <c r="B1234" s="0" t="inlineStr">
         <is>
           <t>攻殻機動隊</t>
         </is>
       </c>
-      <c r="C1234" t="inlineStr">
+      <c r="C1234" s="0" t="inlineStr">
         <is>
           <t>L攻殻機動隊</t>
         </is>
       </c>
     </row>
     <row r="1235">
-      <c r="B1235" t="inlineStr">
+      <c r="B1235" s="0" t="inlineStr">
         <is>
           <t>新鬼武者3</t>
         </is>
       </c>
-      <c r="C1235" t="inlineStr">
+      <c r="C1235" s="0" t="inlineStr">
         <is>
           <t>新鬼武者3</t>
         </is>
       </c>
     </row>
     <row r="1236">
-      <c r="B1236" t="inlineStr">
+      <c r="B1236" s="0" t="inlineStr">
         <is>
           <t>獣王</t>
         </is>
       </c>
-      <c r="C1236" t="inlineStr">
+      <c r="C1236" s="0" t="inlineStr">
         <is>
           <t>獣王</t>
         </is>
       </c>
     </row>
     <row r="1237">
-      <c r="B1237" t="inlineStr">
+      <c r="B1237" s="0" t="inlineStr">
         <is>
           <t>甲鉄城のカバネリ 海門(うなと)決戦</t>
         </is>
       </c>
-      <c r="C1237" t="inlineStr">
+      <c r="C1237" s="0" t="inlineStr">
         <is>
           <t>カバネリ海門決戦</t>
         </is>
       </c>
     </row>
     <row r="1238">
-      <c r="B1238" t="inlineStr">
+      <c r="B1238" s="0" t="inlineStr">
         <is>
           <t>痛いのは嫌なので防御力に極振りしたいと思います。</t>
         </is>
       </c>
-      <c r="C1238" t="inlineStr">
+      <c r="C1238" s="0" t="inlineStr">
         <is>
           <t>防振り</t>
         </is>
       </c>
     </row>
     <row r="1239">
-      <c r="B1239" t="inlineStr">
+      <c r="B1239" s="0" t="inlineStr">
         <is>
           <t>青春ブタ野郎はバニーガール先輩の夢を見ない</t>
         </is>
       </c>
-      <c r="C1239" t="inlineStr">
+      <c r="C1239" s="0" t="inlineStr">
         <is>
           <t>青ブタ</t>
         </is>
       </c>
     </row>
     <row r="1240">
-      <c r="B1240" t="inlineStr">
+      <c r="B1240" s="0" t="inlineStr">
         <is>
           <t>革命機ヴァルヴレイヴ2</t>
         </is>
       </c>
-      <c r="C1240" t="inlineStr">
+      <c r="C1240" s="0" t="inlineStr">
         <is>
           <t>ヴァルヴレイヴ2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1241">
+      <c r="B1241" t="inlineStr">
+        <is>
+          <t>L魔法少女にあこがれて</t>
+        </is>
+      </c>
+      <c r="C1241" t="inlineStr">
+        <is>
+          <t>魔法少女にあこがれて</t>
         </is>
       </c>
     </row>

--- a/機種名変換.xlsx
+++ b/機種名変換.xlsx
@@ -554,7 +554,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1241"/>
+  <dimension ref="A1:C1242"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
     <col width="8.796875" customWidth="1" style="1" min="1" max="1"/>
@@ -15436,14 +15436,26 @@
       </c>
     </row>
     <row r="1241">
-      <c r="B1241" t="inlineStr">
+      <c r="B1241" s="0" t="inlineStr">
         <is>
           <t>L魔法少女にあこがれて</t>
         </is>
       </c>
-      <c r="C1241" t="inlineStr">
+      <c r="C1241" s="0" t="inlineStr">
         <is>
           <t>魔法少女にあこがれて</t>
+        </is>
+      </c>
+    </row>
+    <row r="1242">
+      <c r="B1242" t="inlineStr">
+        <is>
+          <t>沖ドキ!ゴージャス</t>
+        </is>
+      </c>
+      <c r="C1242" t="inlineStr">
+        <is>
+          <t>沖ドキゴージャス25</t>
         </is>
       </c>
     </row>

--- a/機種名変換.xlsx
+++ b/機種名変換.xlsx
@@ -554,7 +554,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1242"/>
+  <dimension ref="A1:C1244"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
     <col width="8.796875" customWidth="1" style="1" min="1" max="1"/>
@@ -15448,14 +15448,38 @@
       </c>
     </row>
     <row r="1242">
-      <c r="B1242" t="inlineStr">
+      <c r="B1242" s="0" t="inlineStr">
         <is>
           <t>沖ドキ!ゴージャス</t>
         </is>
       </c>
-      <c r="C1242" t="inlineStr">
+      <c r="C1242" s="0" t="inlineStr">
         <is>
           <t>沖ドキゴージャス25</t>
+        </is>
+      </c>
+    </row>
+    <row r="1243">
+      <c r="B1243" t="inlineStr">
+        <is>
+          <t>LBクレアの秘宝伝ボーナストリガーver.</t>
+        </is>
+      </c>
+      <c r="C1243" t="inlineStr">
+        <is>
+          <t>クレアの秘宝伝</t>
+        </is>
+      </c>
+    </row>
+    <row r="1244">
+      <c r="B1244" t="inlineStr">
+        <is>
+          <t>ニューパルサーSP4 with 太鼓の達人</t>
+        </is>
+      </c>
+      <c r="C1244" t="inlineStr">
+        <is>
+          <t>ニューパル太鼓</t>
         </is>
       </c>
     </row>

--- a/機種名変換.xlsx
+++ b/機種名変換.xlsx
@@ -554,7 +554,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1244"/>
+  <dimension ref="A1:C1247"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
     <col width="8.796875" customWidth="1" style="1" min="1" max="1"/>
@@ -15460,26 +15460,62 @@
       </c>
     </row>
     <row r="1243">
-      <c r="B1243" t="inlineStr">
+      <c r="B1243" s="0" t="inlineStr">
         <is>
           <t>LBクレアの秘宝伝ボーナストリガーver.</t>
         </is>
       </c>
-      <c r="C1243" t="inlineStr">
+      <c r="C1243" s="0" t="inlineStr">
         <is>
           <t>クレアの秘宝伝</t>
         </is>
       </c>
     </row>
     <row r="1244">
-      <c r="B1244" t="inlineStr">
+      <c r="B1244" s="0" t="inlineStr">
         <is>
           <t>ニューパルサーSP4 with 太鼓の達人</t>
         </is>
       </c>
-      <c r="C1244" t="inlineStr">
+      <c r="C1244" s="0" t="inlineStr">
         <is>
           <t>ニューパル太鼓</t>
+        </is>
+      </c>
+    </row>
+    <row r="1245">
+      <c r="B1245" t="inlineStr">
+        <is>
+          <t>L/SHAMANKING/SS</t>
+        </is>
+      </c>
+      <c r="C1245" t="inlineStr">
+        <is>
+          <t>シャーマンキング</t>
+        </is>
+      </c>
+    </row>
+    <row r="1246">
+      <c r="B1246" t="inlineStr">
+        <is>
+          <t>LシスタークエストCA</t>
+        </is>
+      </c>
+      <c r="C1246" t="inlineStr">
+        <is>
+          <t>シスクエ</t>
+        </is>
+      </c>
+    </row>
+    <row r="1247">
+      <c r="B1247" t="inlineStr">
+        <is>
+          <t>Lシン・エヴァンゲリオン</t>
+        </is>
+      </c>
+      <c r="C1247" t="inlineStr">
+        <is>
+          <t>シンエヴァ</t>
         </is>
       </c>
     </row>

--- a/機種名変換.xlsx
+++ b/機種名変換.xlsx
@@ -554,7 +554,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1247"/>
+  <dimension ref="A1:C1249"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
     <col width="8.796875" customWidth="1" style="1" min="1" max="1"/>
@@ -15484,38 +15484,62 @@
       </c>
     </row>
     <row r="1245">
-      <c r="B1245" t="inlineStr">
+      <c r="B1245" s="0" t="inlineStr">
         <is>
           <t>L/SHAMANKING/SS</t>
         </is>
       </c>
-      <c r="C1245" t="inlineStr">
+      <c r="C1245" s="0" t="inlineStr">
         <is>
           <t>シャーマンキング</t>
         </is>
       </c>
     </row>
     <row r="1246">
-      <c r="B1246" t="inlineStr">
+      <c r="B1246" s="0" t="inlineStr">
         <is>
           <t>LシスタークエストCA</t>
         </is>
       </c>
-      <c r="C1246" t="inlineStr">
+      <c r="C1246" s="0" t="inlineStr">
         <is>
           <t>シスクエ</t>
         </is>
       </c>
     </row>
     <row r="1247">
-      <c r="B1247" t="inlineStr">
+      <c r="B1247" s="0" t="inlineStr">
         <is>
           <t>Lシン・エヴァンゲリオン</t>
         </is>
       </c>
-      <c r="C1247" t="inlineStr">
+      <c r="C1247" s="0" t="inlineStr">
         <is>
           <t>シンエヴァ</t>
+        </is>
+      </c>
+    </row>
+    <row r="1248">
+      <c r="B1248" t="inlineStr">
+        <is>
+          <t>革命機ヴァルヴレイヴ</t>
+        </is>
+      </c>
+      <c r="C1248" t="inlineStr">
+        <is>
+          <t>ヴァルヴレイヴ</t>
+        </is>
+      </c>
+    </row>
+    <row r="1249">
+      <c r="B1249" t="inlineStr">
+        <is>
+          <t>魔法少女にあこがれて</t>
+        </is>
+      </c>
+      <c r="C1249" t="inlineStr">
+        <is>
+          <t>魔法少女にあこがれて</t>
         </is>
       </c>
     </row>

--- a/機種名変換.xlsx
+++ b/機種名変換.xlsx
@@ -554,7 +554,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1249"/>
+  <dimension ref="A1:C1276"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
     <col width="8.796875" customWidth="1" style="1" min="1" max="1"/>
@@ -15520,26 +15520,350 @@
       </c>
     </row>
     <row r="1248">
-      <c r="B1248" t="inlineStr">
+      <c r="B1248" s="0" t="inlineStr">
         <is>
           <t>革命機ヴァルヴレイヴ</t>
         </is>
       </c>
-      <c r="C1248" t="inlineStr">
+      <c r="C1248" s="0" t="inlineStr">
         <is>
           <t>ヴァルヴレイヴ</t>
         </is>
       </c>
     </row>
     <row r="1249">
-      <c r="B1249" t="inlineStr">
+      <c r="B1249" s="0" t="inlineStr">
         <is>
           <t>魔法少女にあこがれて</t>
         </is>
       </c>
-      <c r="C1249" t="inlineStr">
+      <c r="C1249" s="0" t="inlineStr">
         <is>
           <t>魔法少女にあこがれて</t>
+        </is>
+      </c>
+    </row>
+    <row r="1250">
+      <c r="B1250" t="inlineStr">
+        <is>
+          <t>L Re:ゼロ season2PA5</t>
+        </is>
+      </c>
+      <c r="C1250" t="inlineStr">
+        <is>
+          <t>Re:ゼロ2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1251">
+      <c r="B1251" t="inlineStr">
+        <is>
+          <t>L スマスロ真北斗無双 FS</t>
+        </is>
+      </c>
+      <c r="C1251" t="inlineStr">
+        <is>
+          <t>スマスロ北斗無双</t>
+        </is>
+      </c>
+    </row>
+    <row r="1252">
+      <c r="B1252" t="inlineStr">
+        <is>
+          <t>L/オキドキデュオ2/FR</t>
+        </is>
+      </c>
+      <c r="C1252" t="inlineStr">
+        <is>
+          <t>L沖ドキDUO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1253">
+      <c r="B1253" t="inlineStr">
+        <is>
+          <t>L/ソードアート・オンラインII/PA1</t>
+        </is>
+      </c>
+      <c r="C1253" t="inlineStr">
+        <is>
+          <t>SAOII</t>
+        </is>
+      </c>
+    </row>
+    <row r="1254">
+      <c r="B1254" t="inlineStr">
+        <is>
+          <t>LB/シェイクボーナストリガー/A1</t>
+        </is>
+      </c>
+      <c r="C1254" t="inlineStr">
+        <is>
+          <t>LBシェイク</t>
+        </is>
+      </c>
+    </row>
+    <row r="1255">
+      <c r="B1255" t="inlineStr">
+        <is>
+          <t>Lうみねこのなく頃に2A1</t>
+        </is>
+      </c>
+      <c r="C1255" t="inlineStr">
+        <is>
+          <t>うみねこ2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1256">
+      <c r="B1256" t="inlineStr">
+        <is>
+          <t>LとんでもスキルKM</t>
+        </is>
+      </c>
+      <c r="C1256" t="inlineStr">
+        <is>
+          <t>とんスキ</t>
+        </is>
+      </c>
+    </row>
+    <row r="1257">
+      <c r="B1257" t="inlineStr">
+        <is>
+          <t>Lびん娘NY1</t>
+        </is>
+      </c>
+      <c r="C1257" t="inlineStr">
+        <is>
+          <t>びん娘</t>
+        </is>
+      </c>
+    </row>
+    <row r="1258">
+      <c r="B1258" t="inlineStr">
+        <is>
+          <t>Lガールズ&amp;パンツァー最終章H1</t>
+        </is>
+      </c>
+      <c r="C1258" t="inlineStr">
+        <is>
+          <t>ガルパン最終章</t>
+        </is>
+      </c>
+    </row>
+    <row r="1259">
+      <c r="B1259" t="inlineStr">
+        <is>
+          <t>Lスマスロサラリーマン金太郎ET</t>
+        </is>
+      </c>
+      <c r="C1259" t="inlineStr">
+        <is>
+          <t>サラ金</t>
+        </is>
+      </c>
+    </row>
+    <row r="1260">
+      <c r="B1260" t="inlineStr">
+        <is>
+          <t>Lスロット ゾンビランドサガA1</t>
+        </is>
+      </c>
+      <c r="C1260" t="inlineStr">
+        <is>
+          <t>ゾンビランドサガ</t>
+        </is>
+      </c>
+    </row>
+    <row r="1261">
+      <c r="B1261" t="inlineStr">
+        <is>
+          <t>LタクトオーパスM1</t>
+        </is>
+      </c>
+      <c r="C1261" t="inlineStr">
+        <is>
+          <t>タクトオーパス</t>
+        </is>
+      </c>
+    </row>
+    <row r="1262">
+      <c r="B1262" t="inlineStr">
+        <is>
+          <t>Lダンベル何キロ持てる?X</t>
+        </is>
+      </c>
+      <c r="C1262" t="inlineStr">
+        <is>
+          <t>ダン持て</t>
+        </is>
+      </c>
+    </row>
+    <row r="1263">
+      <c r="B1263" t="inlineStr">
+        <is>
+          <t>Lパチスロ花の慶次~佐渡攻めの章~ER</t>
+        </is>
+      </c>
+      <c r="C1263" t="inlineStr">
+        <is>
+          <t>花の慶次佐渡攻め</t>
+        </is>
+      </c>
+    </row>
+    <row r="1264">
+      <c r="B1264" t="inlineStr">
+        <is>
+          <t>LプリズムナナCC</t>
+        </is>
+      </c>
+      <c r="C1264" t="inlineStr">
+        <is>
+          <t>プリズムナナ</t>
+        </is>
+      </c>
+    </row>
+    <row r="1265">
+      <c r="B1265" t="inlineStr">
+        <is>
+          <t>Lマクロスフロンティア4bA</t>
+        </is>
+      </c>
+      <c r="C1265" t="inlineStr">
+        <is>
+          <t>マクロスF4</t>
+        </is>
+      </c>
+    </row>
+    <row r="1266">
+      <c r="B1266" t="inlineStr">
+        <is>
+          <t>LワンパンマンEY</t>
+        </is>
+      </c>
+      <c r="C1266" t="inlineStr">
+        <is>
+          <t>ワンパンマン</t>
+        </is>
+      </c>
+    </row>
+    <row r="1267">
+      <c r="B1267" t="inlineStr">
+        <is>
+          <t>L忍魂参 奥義皆伝ノ章 A3</t>
+        </is>
+      </c>
+      <c r="C1267" t="inlineStr">
+        <is>
+          <t>忍魂参</t>
+        </is>
+      </c>
+    </row>
+    <row r="1268">
+      <c r="B1268" t="inlineStr">
+        <is>
+          <t>L押忍!番長4 A3</t>
+        </is>
+      </c>
+      <c r="C1268" t="inlineStr">
+        <is>
+          <t>番長4</t>
+        </is>
+      </c>
+    </row>
+    <row r="1269">
+      <c r="B1269" t="inlineStr">
+        <is>
+          <t>L犬夜叉2FK</t>
+        </is>
+      </c>
+      <c r="C1269" t="inlineStr">
+        <is>
+          <t>犬夜叉2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1270">
+      <c r="B1270" t="inlineStr">
+        <is>
+          <t>L見える子ちゃんSC</t>
+        </is>
+      </c>
+      <c r="C1270" t="inlineStr">
+        <is>
+          <t>見える子ちゃん</t>
+        </is>
+      </c>
+    </row>
+    <row r="1271">
+      <c r="B1271" t="inlineStr">
+        <is>
+          <t>L邪神ちゃんドロップキックTX</t>
+        </is>
+      </c>
+      <c r="C1271" t="inlineStr">
+        <is>
+          <t>邪神ちゃん</t>
+        </is>
+      </c>
+    </row>
+    <row r="1272">
+      <c r="B1272" t="inlineStr">
+        <is>
+          <t>L魔法少女にあこがれてNP</t>
+        </is>
+      </c>
+      <c r="C1272" t="inlineStr">
+        <is>
+          <t>魔法少女にあこがれて</t>
+        </is>
+      </c>
+    </row>
+    <row r="1273">
+      <c r="B1273" t="inlineStr">
+        <is>
+          <t>S エウレカセブンHIEVO XS</t>
+        </is>
+      </c>
+      <c r="C1273" t="inlineStr">
+        <is>
+          <t>エウレカART</t>
+        </is>
+      </c>
+    </row>
+    <row r="1274">
+      <c r="B1274" t="inlineStr">
+        <is>
+          <t>S/沖ドキ!BLACK/EP</t>
+        </is>
+      </c>
+      <c r="C1274" t="inlineStr">
+        <is>
+          <t>沖ドキBLACK</t>
+        </is>
+      </c>
+    </row>
+    <row r="1275">
+      <c r="B1275" t="inlineStr">
+        <is>
+          <t>SBニューキングハナハナVPA-30</t>
+        </is>
+      </c>
+      <c r="C1275" t="inlineStr">
+        <is>
+          <t>キンハナV30</t>
+        </is>
+      </c>
+    </row>
+    <row r="1276">
+      <c r="B1276" t="inlineStr">
+        <is>
+          <t>S戦国恋姫FC</t>
+        </is>
+      </c>
+      <c r="C1276" t="inlineStr">
+        <is>
+          <t>戦国恋姫</t>
         </is>
       </c>
     </row>

--- a/機種名変換.xlsx
+++ b/機種名変換.xlsx
@@ -554,7 +554,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1276"/>
+  <dimension ref="A1:C1286"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
     <col width="8.796875" customWidth="1" style="1" min="1" max="1"/>
@@ -15544,326 +15544,446 @@
       </c>
     </row>
     <row r="1250">
-      <c r="B1250" t="inlineStr">
+      <c r="B1250" s="0" t="inlineStr">
         <is>
           <t>L Re:ゼロ season2PA5</t>
         </is>
       </c>
-      <c r="C1250" t="inlineStr">
+      <c r="C1250" s="0" t="inlineStr">
         <is>
           <t>Re:ゼロ2</t>
         </is>
       </c>
     </row>
     <row r="1251">
-      <c r="B1251" t="inlineStr">
+      <c r="B1251" s="0" t="inlineStr">
         <is>
           <t>L スマスロ真北斗無双 FS</t>
         </is>
       </c>
-      <c r="C1251" t="inlineStr">
+      <c r="C1251" s="0" t="inlineStr">
         <is>
           <t>スマスロ北斗無双</t>
         </is>
       </c>
     </row>
     <row r="1252">
-      <c r="B1252" t="inlineStr">
+      <c r="B1252" s="0" t="inlineStr">
         <is>
           <t>L/オキドキデュオ2/FR</t>
         </is>
       </c>
-      <c r="C1252" t="inlineStr">
+      <c r="C1252" s="0" t="inlineStr">
         <is>
           <t>L沖ドキDUO</t>
         </is>
       </c>
     </row>
     <row r="1253">
-      <c r="B1253" t="inlineStr">
+      <c r="B1253" s="0" t="inlineStr">
         <is>
           <t>L/ソードアート・オンラインII/PA1</t>
         </is>
       </c>
-      <c r="C1253" t="inlineStr">
+      <c r="C1253" s="0" t="inlineStr">
         <is>
           <t>SAOII</t>
         </is>
       </c>
     </row>
     <row r="1254">
-      <c r="B1254" t="inlineStr">
+      <c r="B1254" s="0" t="inlineStr">
         <is>
           <t>LB/シェイクボーナストリガー/A1</t>
         </is>
       </c>
-      <c r="C1254" t="inlineStr">
+      <c r="C1254" s="0" t="inlineStr">
         <is>
           <t>LBシェイク</t>
         </is>
       </c>
     </row>
     <row r="1255">
-      <c r="B1255" t="inlineStr">
+      <c r="B1255" s="0" t="inlineStr">
         <is>
           <t>Lうみねこのなく頃に2A1</t>
         </is>
       </c>
-      <c r="C1255" t="inlineStr">
+      <c r="C1255" s="0" t="inlineStr">
         <is>
           <t>うみねこ2</t>
         </is>
       </c>
     </row>
     <row r="1256">
-      <c r="B1256" t="inlineStr">
+      <c r="B1256" s="0" t="inlineStr">
         <is>
           <t>LとんでもスキルKM</t>
         </is>
       </c>
-      <c r="C1256" t="inlineStr">
+      <c r="C1256" s="0" t="inlineStr">
         <is>
           <t>とんスキ</t>
         </is>
       </c>
     </row>
     <row r="1257">
-      <c r="B1257" t="inlineStr">
+      <c r="B1257" s="0" t="inlineStr">
         <is>
           <t>Lびん娘NY1</t>
         </is>
       </c>
-      <c r="C1257" t="inlineStr">
+      <c r="C1257" s="0" t="inlineStr">
         <is>
           <t>びん娘</t>
         </is>
       </c>
     </row>
     <row r="1258">
-      <c r="B1258" t="inlineStr">
+      <c r="B1258" s="0" t="inlineStr">
         <is>
           <t>Lガールズ&amp;パンツァー最終章H1</t>
         </is>
       </c>
-      <c r="C1258" t="inlineStr">
+      <c r="C1258" s="0" t="inlineStr">
         <is>
           <t>ガルパン最終章</t>
         </is>
       </c>
     </row>
     <row r="1259">
-      <c r="B1259" t="inlineStr">
+      <c r="B1259" s="0" t="inlineStr">
         <is>
           <t>Lスマスロサラリーマン金太郎ET</t>
         </is>
       </c>
-      <c r="C1259" t="inlineStr">
+      <c r="C1259" s="0" t="inlineStr">
         <is>
           <t>サラ金</t>
         </is>
       </c>
     </row>
     <row r="1260">
-      <c r="B1260" t="inlineStr">
+      <c r="B1260" s="0" t="inlineStr">
         <is>
           <t>Lスロット ゾンビランドサガA1</t>
         </is>
       </c>
-      <c r="C1260" t="inlineStr">
+      <c r="C1260" s="0" t="inlineStr">
         <is>
           <t>ゾンビランドサガ</t>
         </is>
       </c>
     </row>
     <row r="1261">
-      <c r="B1261" t="inlineStr">
+      <c r="B1261" s="0" t="inlineStr">
         <is>
           <t>LタクトオーパスM1</t>
         </is>
       </c>
-      <c r="C1261" t="inlineStr">
+      <c r="C1261" s="0" t="inlineStr">
         <is>
           <t>タクトオーパス</t>
         </is>
       </c>
     </row>
     <row r="1262">
-      <c r="B1262" t="inlineStr">
+      <c r="B1262" s="0" t="inlineStr">
         <is>
           <t>Lダンベル何キロ持てる?X</t>
         </is>
       </c>
-      <c r="C1262" t="inlineStr">
+      <c r="C1262" s="0" t="inlineStr">
         <is>
           <t>ダン持て</t>
         </is>
       </c>
     </row>
     <row r="1263">
-      <c r="B1263" t="inlineStr">
+      <c r="B1263" s="0" t="inlineStr">
         <is>
           <t>Lパチスロ花の慶次~佐渡攻めの章~ER</t>
         </is>
       </c>
-      <c r="C1263" t="inlineStr">
+      <c r="C1263" s="0" t="inlineStr">
         <is>
           <t>花の慶次佐渡攻め</t>
         </is>
       </c>
     </row>
     <row r="1264">
-      <c r="B1264" t="inlineStr">
+      <c r="B1264" s="0" t="inlineStr">
         <is>
           <t>LプリズムナナCC</t>
         </is>
       </c>
-      <c r="C1264" t="inlineStr">
+      <c r="C1264" s="0" t="inlineStr">
         <is>
           <t>プリズムナナ</t>
         </is>
       </c>
     </row>
     <row r="1265">
-      <c r="B1265" t="inlineStr">
+      <c r="B1265" s="0" t="inlineStr">
         <is>
           <t>Lマクロスフロンティア4bA</t>
         </is>
       </c>
-      <c r="C1265" t="inlineStr">
+      <c r="C1265" s="0" t="inlineStr">
         <is>
           <t>マクロスF4</t>
         </is>
       </c>
     </row>
     <row r="1266">
-      <c r="B1266" t="inlineStr">
+      <c r="B1266" s="0" t="inlineStr">
         <is>
           <t>LワンパンマンEY</t>
         </is>
       </c>
-      <c r="C1266" t="inlineStr">
+      <c r="C1266" s="0" t="inlineStr">
         <is>
           <t>ワンパンマン</t>
         </is>
       </c>
     </row>
     <row r="1267">
-      <c r="B1267" t="inlineStr">
+      <c r="B1267" s="0" t="inlineStr">
         <is>
           <t>L忍魂参 奥義皆伝ノ章 A3</t>
         </is>
       </c>
-      <c r="C1267" t="inlineStr">
+      <c r="C1267" s="0" t="inlineStr">
         <is>
           <t>忍魂参</t>
         </is>
       </c>
     </row>
     <row r="1268">
-      <c r="B1268" t="inlineStr">
+      <c r="B1268" s="0" t="inlineStr">
         <is>
           <t>L押忍!番長4 A3</t>
         </is>
       </c>
-      <c r="C1268" t="inlineStr">
+      <c r="C1268" s="0" t="inlineStr">
         <is>
           <t>番長4</t>
         </is>
       </c>
     </row>
     <row r="1269">
-      <c r="B1269" t="inlineStr">
+      <c r="B1269" s="0" t="inlineStr">
         <is>
           <t>L犬夜叉2FK</t>
         </is>
       </c>
-      <c r="C1269" t="inlineStr">
+      <c r="C1269" s="0" t="inlineStr">
         <is>
           <t>犬夜叉2</t>
         </is>
       </c>
     </row>
     <row r="1270">
-      <c r="B1270" t="inlineStr">
+      <c r="B1270" s="0" t="inlineStr">
         <is>
           <t>L見える子ちゃんSC</t>
         </is>
       </c>
-      <c r="C1270" t="inlineStr">
+      <c r="C1270" s="0" t="inlineStr">
         <is>
           <t>見える子ちゃん</t>
         </is>
       </c>
     </row>
     <row r="1271">
-      <c r="B1271" t="inlineStr">
+      <c r="B1271" s="0" t="inlineStr">
         <is>
           <t>L邪神ちゃんドロップキックTX</t>
         </is>
       </c>
-      <c r="C1271" t="inlineStr">
+      <c r="C1271" s="0" t="inlineStr">
         <is>
           <t>邪神ちゃん</t>
         </is>
       </c>
     </row>
     <row r="1272">
-      <c r="B1272" t="inlineStr">
+      <c r="B1272" s="0" t="inlineStr">
         <is>
           <t>L魔法少女にあこがれてNP</t>
         </is>
       </c>
-      <c r="C1272" t="inlineStr">
+      <c r="C1272" s="0" t="inlineStr">
         <is>
           <t>魔法少女にあこがれて</t>
         </is>
       </c>
     </row>
     <row r="1273">
-      <c r="B1273" t="inlineStr">
+      <c r="B1273" s="0" t="inlineStr">
         <is>
           <t>S エウレカセブンHIEVO XS</t>
         </is>
       </c>
-      <c r="C1273" t="inlineStr">
+      <c r="C1273" s="0" t="inlineStr">
         <is>
           <t>エウレカART</t>
         </is>
       </c>
     </row>
     <row r="1274">
-      <c r="B1274" t="inlineStr">
+      <c r="B1274" s="0" t="inlineStr">
         <is>
           <t>S/沖ドキ!BLACK/EP</t>
         </is>
       </c>
-      <c r="C1274" t="inlineStr">
+      <c r="C1274" s="0" t="inlineStr">
         <is>
           <t>沖ドキBLACK</t>
         </is>
       </c>
     </row>
     <row r="1275">
-      <c r="B1275" t="inlineStr">
+      <c r="B1275" s="0" t="inlineStr">
         <is>
           <t>SBニューキングハナハナVPA-30</t>
         </is>
       </c>
-      <c r="C1275" t="inlineStr">
+      <c r="C1275" s="0" t="inlineStr">
         <is>
           <t>キンハナV30</t>
         </is>
       </c>
     </row>
     <row r="1276">
-      <c r="B1276" t="inlineStr">
+      <c r="B1276" s="0" t="inlineStr">
         <is>
           <t>S戦国恋姫FC</t>
         </is>
       </c>
-      <c r="C1276" t="inlineStr">
+      <c r="C1276" s="0" t="inlineStr">
         <is>
           <t>戦国恋姫</t>
+        </is>
+      </c>
+    </row>
+    <row r="1277">
+      <c r="B1277" t="inlineStr">
+        <is>
+          <t>Lゴッドイーター リザレクション2</t>
+        </is>
+      </c>
+      <c r="C1277" t="inlineStr">
+        <is>
+          <t>ゴッドイーター</t>
+        </is>
+      </c>
+    </row>
+    <row r="1278">
+      <c r="B1278" t="inlineStr">
+        <is>
+          <t>Lスマスロ北斗2</t>
+        </is>
+      </c>
+      <c r="C1278" t="inlineStr">
+        <is>
+          <t>スマスロ北斗の拳</t>
+        </is>
+      </c>
+    </row>
+    <row r="1279">
+      <c r="B1279" t="inlineStr">
+        <is>
+          <t>Lソードアート・オンライン1</t>
+        </is>
+      </c>
+      <c r="C1279" t="inlineStr">
+        <is>
+          <t>SAO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1280">
+      <c r="B1280" t="inlineStr">
+        <is>
+          <t>L一方通行トアル魔術禁書目録</t>
+        </is>
+      </c>
+      <c r="C1280" t="inlineStr">
+        <is>
+          <t>一方通行</t>
+        </is>
+      </c>
+    </row>
+    <row r="1281">
+      <c r="B1281" t="inlineStr">
+        <is>
+          <t>けものフレンズ</t>
+        </is>
+      </c>
+      <c r="C1281" t="inlineStr">
+        <is>
+          <t>けものフレンズ</t>
+        </is>
+      </c>
+    </row>
+    <row r="1282">
+      <c r="B1282" t="inlineStr">
+        <is>
+          <t>アクエリオン ALL STARS</t>
+        </is>
+      </c>
+      <c r="C1282" t="inlineStr">
+        <is>
+          <t>アクエリオンALL STARS</t>
+        </is>
+      </c>
+    </row>
+    <row r="1283">
+      <c r="B1283" t="inlineStr">
+        <is>
+          <t>ドリフターズ</t>
+        </is>
+      </c>
+      <c r="C1283" t="inlineStr">
+        <is>
+          <t>ドリフターズ</t>
+        </is>
+      </c>
+    </row>
+    <row r="1284">
+      <c r="B1284" t="inlineStr">
+        <is>
+          <t>政宗 戦極</t>
+        </is>
+      </c>
+      <c r="C1284" t="inlineStr">
+        <is>
+          <t>政宗</t>
+        </is>
+      </c>
+    </row>
+    <row r="1285">
+      <c r="B1285" t="inlineStr">
+        <is>
+          <t>盾の勇者の成り上がり</t>
+        </is>
+      </c>
+      <c r="C1285" t="inlineStr">
+        <is>
+          <t>盾の勇者</t>
+        </is>
+      </c>
+    </row>
+    <row r="1286">
+      <c r="B1286" t="inlineStr">
+        <is>
+          <t>魔法少女育成計画</t>
+        </is>
+      </c>
+      <c r="C1286" t="inlineStr">
+        <is>
+          <t>魔法少女育成計画</t>
         </is>
       </c>
     </row>

--- a/機種名変換.xlsx
+++ b/機種名変換.xlsx
@@ -554,7 +554,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1286"/>
+  <dimension ref="A1:C1287"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
     <col width="8.796875" customWidth="1" style="1" min="1" max="1"/>
@@ -15868,122 +15868,134 @@
       </c>
     </row>
     <row r="1277">
-      <c r="B1277" t="inlineStr">
+      <c r="B1277" s="0" t="inlineStr">
         <is>
           <t>Lゴッドイーター リザレクション2</t>
         </is>
       </c>
-      <c r="C1277" t="inlineStr">
+      <c r="C1277" s="0" t="inlineStr">
         <is>
           <t>ゴッドイーター</t>
         </is>
       </c>
     </row>
     <row r="1278">
-      <c r="B1278" t="inlineStr">
+      <c r="B1278" s="0" t="inlineStr">
         <is>
           <t>Lスマスロ北斗2</t>
         </is>
       </c>
-      <c r="C1278" t="inlineStr">
+      <c r="C1278" s="0" t="inlineStr">
         <is>
           <t>スマスロ北斗の拳</t>
         </is>
       </c>
     </row>
     <row r="1279">
-      <c r="B1279" t="inlineStr">
+      <c r="B1279" s="0" t="inlineStr">
         <is>
           <t>Lソードアート・オンライン1</t>
         </is>
       </c>
-      <c r="C1279" t="inlineStr">
+      <c r="C1279" s="0" t="inlineStr">
         <is>
           <t>SAO</t>
         </is>
       </c>
     </row>
     <row r="1280">
-      <c r="B1280" t="inlineStr">
+      <c r="B1280" s="0" t="inlineStr">
         <is>
           <t>L一方通行トアル魔術禁書目録</t>
         </is>
       </c>
-      <c r="C1280" t="inlineStr">
+      <c r="C1280" s="0" t="inlineStr">
         <is>
           <t>一方通行</t>
         </is>
       </c>
     </row>
     <row r="1281">
-      <c r="B1281" t="inlineStr">
+      <c r="B1281" s="0" t="inlineStr">
         <is>
           <t>けものフレンズ</t>
         </is>
       </c>
-      <c r="C1281" t="inlineStr">
+      <c r="C1281" s="0" t="inlineStr">
         <is>
           <t>けものフレンズ</t>
         </is>
       </c>
     </row>
     <row r="1282">
-      <c r="B1282" t="inlineStr">
+      <c r="B1282" s="0" t="inlineStr">
         <is>
           <t>アクエリオン ALL STARS</t>
         </is>
       </c>
-      <c r="C1282" t="inlineStr">
+      <c r="C1282" s="0" t="inlineStr">
         <is>
           <t>アクエリオンALL STARS</t>
         </is>
       </c>
     </row>
     <row r="1283">
-      <c r="B1283" t="inlineStr">
+      <c r="B1283" s="0" t="inlineStr">
         <is>
           <t>ドリフターズ</t>
         </is>
       </c>
-      <c r="C1283" t="inlineStr">
+      <c r="C1283" s="0" t="inlineStr">
         <is>
           <t>ドリフターズ</t>
         </is>
       </c>
     </row>
     <row r="1284">
-      <c r="B1284" t="inlineStr">
+      <c r="B1284" s="0" t="inlineStr">
         <is>
           <t>政宗 戦極</t>
         </is>
       </c>
-      <c r="C1284" t="inlineStr">
+      <c r="C1284" s="0" t="inlineStr">
         <is>
           <t>政宗</t>
         </is>
       </c>
     </row>
     <row r="1285">
-      <c r="B1285" t="inlineStr">
+      <c r="B1285" s="0" t="inlineStr">
         <is>
           <t>盾の勇者の成り上がり</t>
         </is>
       </c>
-      <c r="C1285" t="inlineStr">
+      <c r="C1285" s="0" t="inlineStr">
         <is>
           <t>盾の勇者</t>
         </is>
       </c>
     </row>
     <row r="1286">
-      <c r="B1286" t="inlineStr">
+      <c r="B1286" s="0" t="inlineStr">
         <is>
           <t>魔法少女育成計画</t>
         </is>
       </c>
-      <c r="C1286" t="inlineStr">
+      <c r="C1286" s="0" t="inlineStr">
         <is>
           <t>魔法少女育成計画</t>
+        </is>
+      </c>
+    </row>
+    <row r="1287">
+      <c r="B1287" t="inlineStr">
+        <is>
+          <t>Lスマスロ北斗1</t>
+        </is>
+      </c>
+      <c r="C1287" t="inlineStr">
+        <is>
+          <t>スマスロ北斗の拳</t>
         </is>
       </c>
     </row>

--- a/機種名変換.xlsx
+++ b/機種名変換.xlsx
@@ -554,7 +554,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1287"/>
+  <dimension ref="A1:C1290"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
     <col width="8.796875" customWidth="1" style="1" min="1" max="1"/>
@@ -15988,14 +15988,50 @@
       </c>
     </row>
     <row r="1287">
-      <c r="B1287" t="inlineStr">
+      <c r="B1287" s="0" t="inlineStr">
         <is>
           <t>Lスマスロ北斗1</t>
         </is>
       </c>
-      <c r="C1287" t="inlineStr">
+      <c r="C1287" s="0" t="inlineStr">
         <is>
           <t>スマスロ北斗の拳</t>
+        </is>
+      </c>
+    </row>
+    <row r="1288">
+      <c r="B1288" t="inlineStr">
+        <is>
+          <t>Lヨウコソ実力至上主義ノ教室ヘ</t>
+        </is>
+      </c>
+      <c r="C1288" t="inlineStr">
+        <is>
+          <t>よう実</t>
+        </is>
+      </c>
+    </row>
+    <row r="1289">
+      <c r="B1289" t="inlineStr">
+        <is>
+          <t>L桃太郎電鉄 パチスロも定番!</t>
+        </is>
+      </c>
+      <c r="C1289" t="inlineStr">
+        <is>
+          <t>桃太郎電鉄</t>
+        </is>
+      </c>
+    </row>
+    <row r="1290">
+      <c r="B1290" t="inlineStr">
+        <is>
+          <t>SLOTマッピー</t>
+        </is>
+      </c>
+      <c r="C1290" t="inlineStr">
+        <is>
+          <t>マッピー</t>
         </is>
       </c>
     </row>

--- a/機種名変換.xlsx
+++ b/機種名変換.xlsx
@@ -554,7 +554,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1290"/>
+  <dimension ref="A1:C1311"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
     <col width="8.796875" customWidth="1" style="1" min="1" max="1"/>
@@ -16000,38 +16000,290 @@
       </c>
     </row>
     <row r="1288">
-      <c r="B1288" t="inlineStr">
+      <c r="B1288" s="0" t="inlineStr">
         <is>
           <t>Lヨウコソ実力至上主義ノ教室ヘ</t>
         </is>
       </c>
-      <c r="C1288" t="inlineStr">
+      <c r="C1288" s="0" t="inlineStr">
         <is>
           <t>よう実</t>
         </is>
       </c>
     </row>
     <row r="1289">
-      <c r="B1289" t="inlineStr">
+      <c r="B1289" s="0" t="inlineStr">
         <is>
           <t>L桃太郎電鉄 パチスロも定番!</t>
         </is>
       </c>
-      <c r="C1289" t="inlineStr">
+      <c r="C1289" s="0" t="inlineStr">
         <is>
           <t>桃太郎電鉄</t>
         </is>
       </c>
     </row>
     <row r="1290">
-      <c r="B1290" t="inlineStr">
+      <c r="B1290" s="0" t="inlineStr">
         <is>
           <t>SLOTマッピー</t>
         </is>
       </c>
-      <c r="C1290" t="inlineStr">
+      <c r="C1290" s="0" t="inlineStr">
         <is>
           <t>マッピー</t>
+        </is>
+      </c>
+    </row>
+    <row r="1291">
+      <c r="B1291" t="inlineStr">
+        <is>
+          <t>L ToLOVEるダークネス TRANCE</t>
+        </is>
+      </c>
+      <c r="C1291" t="inlineStr">
+        <is>
+          <t>ToLOVEるトランス</t>
+        </is>
+      </c>
+    </row>
+    <row r="1292">
+      <c r="B1292" t="inlineStr">
+        <is>
+          <t>L スマスロ ゴッドイーター リザレクション SLED</t>
+        </is>
+      </c>
+      <c r="C1292" t="inlineStr">
+        <is>
+          <t>ゴッドイーター</t>
+        </is>
+      </c>
+    </row>
+    <row r="1293">
+      <c r="B1293" t="inlineStr">
+        <is>
+          <t>L スマスロマギアレコード</t>
+        </is>
+      </c>
+      <c r="C1293" t="inlineStr">
+        <is>
+          <t>マギレコ</t>
+        </is>
+      </c>
+    </row>
+    <row r="1294">
+      <c r="B1294" t="inlineStr">
+        <is>
+          <t>L スマスロモンキーターンV CE</t>
+        </is>
+      </c>
+      <c r="C1294" t="inlineStr">
+        <is>
+          <t>モンキーターンV</t>
+        </is>
+      </c>
+    </row>
+    <row r="1295">
+      <c r="B1295" t="inlineStr">
+        <is>
+          <t>L スマスロ北斗の拳 AD XR</t>
+        </is>
+      </c>
+      <c r="C1295" t="inlineStr">
+        <is>
+          <t>スマスロ北斗の拳</t>
+        </is>
+      </c>
+    </row>
+    <row r="1296">
+      <c r="B1296" t="inlineStr">
+        <is>
+          <t>LB スマスロ サンダーV HA</t>
+        </is>
+      </c>
+      <c r="C1296" t="inlineStr">
+        <is>
+          <t>LBサンダーV</t>
+        </is>
+      </c>
+    </row>
+    <row r="1297">
+      <c r="B1297" t="inlineStr">
+        <is>
+          <t>LB/クレアの秘宝伝BTver./A2</t>
+        </is>
+      </c>
+      <c r="C1297" t="inlineStr">
+        <is>
+          <t>クレアの秘宝伝</t>
+        </is>
+      </c>
+    </row>
+    <row r="1298">
+      <c r="B1298" t="inlineStr">
+        <is>
+          <t>LBアレックスブライトBA</t>
+        </is>
+      </c>
+      <c r="C1298" t="inlineStr">
+        <is>
+          <t>アレックスB</t>
+        </is>
+      </c>
+    </row>
+    <row r="1299">
+      <c r="B1299" t="inlineStr">
+        <is>
+          <t>LBタコスロBD</t>
+        </is>
+      </c>
+      <c r="C1299" t="inlineStr">
+        <is>
+          <t>タコスロ</t>
+        </is>
+      </c>
+    </row>
+    <row r="1300">
+      <c r="B1300" t="inlineStr">
+        <is>
+          <t>Lスマスロパリピ孔明YE05H</t>
+        </is>
+      </c>
+      <c r="C1300" t="inlineStr">
+        <is>
+          <t>パリピ孔明</t>
+        </is>
+      </c>
+    </row>
+    <row r="1301">
+      <c r="B1301" t="inlineStr">
+        <is>
+          <t>Lスマスロ獣王XZ</t>
+        </is>
+      </c>
+      <c r="C1301" t="inlineStr">
+        <is>
+          <t>獣王</t>
+        </is>
+      </c>
+    </row>
+    <row r="1302">
+      <c r="B1302" t="inlineStr">
+        <is>
+          <t>Lソードアート・オンラインII PA1</t>
+        </is>
+      </c>
+      <c r="C1302" t="inlineStr">
+        <is>
+          <t>SAOII</t>
+        </is>
+      </c>
+    </row>
+    <row r="1303">
+      <c r="B1303" t="inlineStr">
+        <is>
+          <t>Lリコリス・リコイルKX</t>
+        </is>
+      </c>
+      <c r="C1303" t="inlineStr">
+        <is>
+          <t>リコリス</t>
+        </is>
+      </c>
+    </row>
+    <row r="1304">
+      <c r="B1304" t="inlineStr">
+        <is>
+          <t>LワールドダイスターPA3</t>
+        </is>
+      </c>
+      <c r="C1304" t="inlineStr">
+        <is>
+          <t>ワールドダイスター</t>
+        </is>
+      </c>
+    </row>
+    <row r="1305">
+      <c r="B1305" t="inlineStr">
+        <is>
+          <t>L彼女、お借りします bK</t>
+        </is>
+      </c>
+      <c r="C1305" t="inlineStr">
+        <is>
+          <t>かのかり</t>
+        </is>
+      </c>
+    </row>
+    <row r="1306">
+      <c r="B1306" t="inlineStr">
+        <is>
+          <t>L転生王女と天才令嬢S3</t>
+        </is>
+      </c>
+      <c r="C1306" t="inlineStr">
+        <is>
+          <t>転生王女と天才令嬢</t>
+        </is>
+      </c>
+    </row>
+    <row r="1307">
+      <c r="B1307" t="inlineStr">
+        <is>
+          <t>S ウルトラミラクルジャグラー KT</t>
+        </is>
+      </c>
+      <c r="C1307" t="inlineStr">
+        <is>
+          <t>ウルトラミラジャグ</t>
+        </is>
+      </c>
+    </row>
+    <row r="1308">
+      <c r="B1308" t="inlineStr">
+        <is>
+          <t>S ジャグラーガールズSS KH</t>
+        </is>
+      </c>
+      <c r="C1308" t="inlineStr">
+        <is>
+          <t>ジャグラーガールズ</t>
+        </is>
+      </c>
+    </row>
+    <row r="1309">
+      <c r="B1309" t="inlineStr">
+        <is>
+          <t>S パチスロ交響詩篇エウレカセブン</t>
+        </is>
+      </c>
+      <c r="C1309" t="inlineStr">
+        <is>
+          <t>エウレカART</t>
+        </is>
+      </c>
+    </row>
+    <row r="1310">
+      <c r="B1310" t="inlineStr">
+        <is>
+          <t>S 沖ドキ!BLACK EP</t>
+        </is>
+      </c>
+      <c r="C1310" t="inlineStr">
+        <is>
+          <t>沖ドキBLACK</t>
+        </is>
+      </c>
+    </row>
+    <row r="1311">
+      <c r="B1311" t="inlineStr">
+        <is>
+          <t>S 沖ドキ!GOLD-30 LS</t>
+        </is>
+      </c>
+      <c r="C1311" t="inlineStr">
+        <is>
+          <t>沖ドキGOLD30</t>
         </is>
       </c>
     </row>

--- a/機種名変換.xlsx
+++ b/機種名変換.xlsx
@@ -554,7 +554,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1311"/>
+  <dimension ref="A1:C1325"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
     <col width="8.796875" customWidth="1" style="1" min="1" max="1"/>
@@ -16036,254 +16036,422 @@
       </c>
     </row>
     <row r="1291">
-      <c r="B1291" t="inlineStr">
+      <c r="B1291" s="0" t="inlineStr">
         <is>
           <t>L ToLOVEるダークネス TRANCE</t>
         </is>
       </c>
-      <c r="C1291" t="inlineStr">
+      <c r="C1291" s="0" t="inlineStr">
         <is>
           <t>ToLOVEるトランス</t>
         </is>
       </c>
     </row>
     <row r="1292">
-      <c r="B1292" t="inlineStr">
+      <c r="B1292" s="0" t="inlineStr">
         <is>
           <t>L スマスロ ゴッドイーター リザレクション SLED</t>
         </is>
       </c>
-      <c r="C1292" t="inlineStr">
+      <c r="C1292" s="0" t="inlineStr">
         <is>
           <t>ゴッドイーター</t>
         </is>
       </c>
     </row>
     <row r="1293">
-      <c r="B1293" t="inlineStr">
+      <c r="B1293" s="0" t="inlineStr">
         <is>
           <t>L スマスロマギアレコード</t>
         </is>
       </c>
-      <c r="C1293" t="inlineStr">
+      <c r="C1293" s="0" t="inlineStr">
         <is>
           <t>マギレコ</t>
         </is>
       </c>
     </row>
     <row r="1294">
-      <c r="B1294" t="inlineStr">
+      <c r="B1294" s="0" t="inlineStr">
         <is>
           <t>L スマスロモンキーターンV CE</t>
         </is>
       </c>
-      <c r="C1294" t="inlineStr">
+      <c r="C1294" s="0" t="inlineStr">
         <is>
           <t>モンキーターンV</t>
         </is>
       </c>
     </row>
     <row r="1295">
-      <c r="B1295" t="inlineStr">
+      <c r="B1295" s="0" t="inlineStr">
         <is>
           <t>L スマスロ北斗の拳 AD XR</t>
         </is>
       </c>
-      <c r="C1295" t="inlineStr">
+      <c r="C1295" s="0" t="inlineStr">
         <is>
           <t>スマスロ北斗の拳</t>
         </is>
       </c>
     </row>
     <row r="1296">
-      <c r="B1296" t="inlineStr">
+      <c r="B1296" s="0" t="inlineStr">
         <is>
           <t>LB スマスロ サンダーV HA</t>
         </is>
       </c>
-      <c r="C1296" t="inlineStr">
+      <c r="C1296" s="0" t="inlineStr">
         <is>
           <t>LBサンダーV</t>
         </is>
       </c>
     </row>
     <row r="1297">
-      <c r="B1297" t="inlineStr">
+      <c r="B1297" s="0" t="inlineStr">
         <is>
           <t>LB/クレアの秘宝伝BTver./A2</t>
         </is>
       </c>
-      <c r="C1297" t="inlineStr">
+      <c r="C1297" s="0" t="inlineStr">
         <is>
           <t>クレアの秘宝伝</t>
         </is>
       </c>
     </row>
     <row r="1298">
-      <c r="B1298" t="inlineStr">
+      <c r="B1298" s="0" t="inlineStr">
         <is>
           <t>LBアレックスブライトBA</t>
         </is>
       </c>
-      <c r="C1298" t="inlineStr">
+      <c r="C1298" s="0" t="inlineStr">
         <is>
           <t>アレックスB</t>
         </is>
       </c>
     </row>
     <row r="1299">
-      <c r="B1299" t="inlineStr">
+      <c r="B1299" s="0" t="inlineStr">
         <is>
           <t>LBタコスロBD</t>
         </is>
       </c>
-      <c r="C1299" t="inlineStr">
+      <c r="C1299" s="0" t="inlineStr">
         <is>
           <t>タコスロ</t>
         </is>
       </c>
     </row>
     <row r="1300">
-      <c r="B1300" t="inlineStr">
+      <c r="B1300" s="0" t="inlineStr">
         <is>
           <t>Lスマスロパリピ孔明YE05H</t>
         </is>
       </c>
-      <c r="C1300" t="inlineStr">
+      <c r="C1300" s="0" t="inlineStr">
         <is>
           <t>パリピ孔明</t>
         </is>
       </c>
     </row>
     <row r="1301">
-      <c r="B1301" t="inlineStr">
+      <c r="B1301" s="0" t="inlineStr">
         <is>
           <t>Lスマスロ獣王XZ</t>
         </is>
       </c>
-      <c r="C1301" t="inlineStr">
+      <c r="C1301" s="0" t="inlineStr">
         <is>
           <t>獣王</t>
         </is>
       </c>
     </row>
     <row r="1302">
-      <c r="B1302" t="inlineStr">
+      <c r="B1302" s="0" t="inlineStr">
         <is>
           <t>Lソードアート・オンラインII PA1</t>
         </is>
       </c>
-      <c r="C1302" t="inlineStr">
+      <c r="C1302" s="0" t="inlineStr">
         <is>
           <t>SAOII</t>
         </is>
       </c>
     </row>
     <row r="1303">
-      <c r="B1303" t="inlineStr">
+      <c r="B1303" s="0" t="inlineStr">
         <is>
           <t>Lリコリス・リコイルKX</t>
         </is>
       </c>
-      <c r="C1303" t="inlineStr">
+      <c r="C1303" s="0" t="inlineStr">
         <is>
           <t>リコリス</t>
         </is>
       </c>
     </row>
     <row r="1304">
-      <c r="B1304" t="inlineStr">
+      <c r="B1304" s="0" t="inlineStr">
         <is>
           <t>LワールドダイスターPA3</t>
         </is>
       </c>
-      <c r="C1304" t="inlineStr">
+      <c r="C1304" s="0" t="inlineStr">
         <is>
           <t>ワールドダイスター</t>
         </is>
       </c>
     </row>
     <row r="1305">
-      <c r="B1305" t="inlineStr">
+      <c r="B1305" s="0" t="inlineStr">
         <is>
           <t>L彼女、お借りします bK</t>
         </is>
       </c>
-      <c r="C1305" t="inlineStr">
+      <c r="C1305" s="0" t="inlineStr">
         <is>
           <t>かのかり</t>
         </is>
       </c>
     </row>
     <row r="1306">
-      <c r="B1306" t="inlineStr">
+      <c r="B1306" s="0" t="inlineStr">
         <is>
           <t>L転生王女と天才令嬢S3</t>
         </is>
       </c>
-      <c r="C1306" t="inlineStr">
+      <c r="C1306" s="0" t="inlineStr">
         <is>
           <t>転生王女と天才令嬢</t>
         </is>
       </c>
     </row>
     <row r="1307">
-      <c r="B1307" t="inlineStr">
+      <c r="B1307" s="0" t="inlineStr">
         <is>
           <t>S ウルトラミラクルジャグラー KT</t>
         </is>
       </c>
-      <c r="C1307" t="inlineStr">
+      <c r="C1307" s="0" t="inlineStr">
         <is>
           <t>ウルトラミラジャグ</t>
         </is>
       </c>
     </row>
     <row r="1308">
-      <c r="B1308" t="inlineStr">
+      <c r="B1308" s="0" t="inlineStr">
         <is>
           <t>S ジャグラーガールズSS KH</t>
         </is>
       </c>
-      <c r="C1308" t="inlineStr">
+      <c r="C1308" s="0" t="inlineStr">
         <is>
           <t>ジャグラーガールズ</t>
         </is>
       </c>
     </row>
     <row r="1309">
-      <c r="B1309" t="inlineStr">
+      <c r="B1309" s="0" t="inlineStr">
         <is>
           <t>S パチスロ交響詩篇エウレカセブン</t>
         </is>
       </c>
-      <c r="C1309" t="inlineStr">
+      <c r="C1309" s="0" t="inlineStr">
         <is>
           <t>エウレカART</t>
         </is>
       </c>
     </row>
     <row r="1310">
-      <c r="B1310" t="inlineStr">
+      <c r="B1310" s="0" t="inlineStr">
         <is>
           <t>S 沖ドキ!BLACK EP</t>
         </is>
       </c>
-      <c r="C1310" t="inlineStr">
+      <c r="C1310" s="0" t="inlineStr">
         <is>
           <t>沖ドキBLACK</t>
         </is>
       </c>
     </row>
     <row r="1311">
-      <c r="B1311" t="inlineStr">
+      <c r="B1311" s="0" t="inlineStr">
         <is>
           <t>S 沖ドキ!GOLD-30 LS</t>
         </is>
       </c>
-      <c r="C1311" t="inlineStr">
+      <c r="C1311" s="0" t="inlineStr">
         <is>
           <t>沖ドキGOLD30</t>
+        </is>
+      </c>
+    </row>
+    <row r="1312">
+      <c r="B1312" t="inlineStr">
+        <is>
+          <t>L ToLOVEるダークネスS8</t>
+        </is>
+      </c>
+      <c r="C1312" t="inlineStr">
+        <is>
+          <t>ToLOVEるトランス</t>
+        </is>
+      </c>
+    </row>
+    <row r="1313">
+      <c r="B1313" t="inlineStr">
+        <is>
+          <t>L バンドリ! S11</t>
+        </is>
+      </c>
+      <c r="C1313" t="inlineStr">
+        <is>
+          <t>バンドリ</t>
+        </is>
+      </c>
+    </row>
+    <row r="1314">
+      <c r="B1314" t="inlineStr">
+        <is>
+          <t>L/ギルティクラウン2/XF</t>
+        </is>
+      </c>
+      <c r="C1314" t="inlineStr">
+        <is>
+          <t>ギルクラ2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1315">
+      <c r="B1315" t="inlineStr">
+        <is>
+          <t>LB不二子M2</t>
+        </is>
+      </c>
+      <c r="C1315" t="inlineStr">
+        <is>
+          <t>LB不二子</t>
+        </is>
+      </c>
+    </row>
+    <row r="1316">
+      <c r="B1316" t="inlineStr">
+        <is>
+          <t>LRe:ゼロから始める異世界生活2PA5</t>
+        </is>
+      </c>
+      <c r="C1316" t="inlineStr">
+        <is>
+          <t>Re:ゼロ2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1317">
+      <c r="B1317" t="inlineStr">
+        <is>
+          <t>Lダーリン・イン・ザ・フランキスSA</t>
+        </is>
+      </c>
+      <c r="C1317" t="inlineStr">
+        <is>
+          <t>ダリフラ</t>
+        </is>
+      </c>
+    </row>
+    <row r="1318">
+      <c r="B1318" t="inlineStr">
+        <is>
+          <t>LバーディーウイングBC</t>
+        </is>
+      </c>
+      <c r="C1318" t="inlineStr">
+        <is>
+          <t>BIRDIE WING</t>
+        </is>
+      </c>
+    </row>
+    <row r="1319">
+      <c r="B1319" t="inlineStr">
+        <is>
+          <t>Lパチスロアイドルマスター ミリオンライブHC</t>
+        </is>
+      </c>
+      <c r="C1319" t="inlineStr">
+        <is>
+          <t>アイマス</t>
+        </is>
+      </c>
+    </row>
+    <row r="1320">
+      <c r="B1320" t="inlineStr">
+        <is>
+          <t>LローティスTN</t>
+        </is>
+      </c>
+      <c r="C1320" t="inlineStr">
+        <is>
+          <t>ローティス</t>
+        </is>
+      </c>
+    </row>
+    <row r="1321">
+      <c r="B1321" t="inlineStr">
+        <is>
+          <t>L反逆/復活のルルーシュZS</t>
+        </is>
+      </c>
+      <c r="C1321" t="inlineStr">
+        <is>
+          <t>ギアス復活</t>
+        </is>
+      </c>
+    </row>
+    <row r="1322">
+      <c r="B1322" t="inlineStr">
+        <is>
+          <t>L虚構推理ST</t>
+        </is>
+      </c>
+      <c r="C1322" t="inlineStr">
+        <is>
+          <t>虚構推理</t>
+        </is>
+      </c>
+    </row>
+    <row r="1323">
+      <c r="B1323" t="inlineStr">
+        <is>
+          <t>L転生王女と天才令嬢の魔法革命S3</t>
+        </is>
+      </c>
+      <c r="C1323" t="inlineStr">
+        <is>
+          <t>転生王女と天才令嬢</t>
+        </is>
+      </c>
+    </row>
+    <row r="1324">
+      <c r="B1324" t="inlineStr">
+        <is>
+          <t>S ファミスタ回胴版!! FB</t>
+        </is>
+      </c>
+      <c r="C1324" t="inlineStr">
+        <is>
+          <t>ファミスタ回胴版</t>
+        </is>
+      </c>
+    </row>
+    <row r="1325">
+      <c r="B1325" t="inlineStr">
+        <is>
+          <t>S 沖ドキ!GOLD GS</t>
+        </is>
+      </c>
+      <c r="C1325" t="inlineStr">
+        <is>
+          <t>沖ドキGOLD</t>
         </is>
       </c>
     </row>
